--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Colombia_P" displayName="AveragesTable_Colombia_P" ref="A1:EC21" headerRowCount="1">
   <autoFilter ref="A1:EC21"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>20</v>
@@ -2971,82 +2971,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="H6" t="n">
-        <v>88.56</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>5.89</v>
+        <v>5.63</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>36.89</v>
+        <v>36.84</v>
       </c>
       <c r="N6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="P6" t="n">
-        <v>10.28</v>
+        <v>10.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.89</v>
+        <v>7.53</v>
       </c>
       <c r="R6" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>54.33</v>
+        <v>54.58</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.17</v>
+        <v>11.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.33</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AF6" t="n">
         <v>0.05</v>
@@ -3130,70 +3130,70 @@
         <v>2.65</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.32</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="BR6" t="n">
-        <v>84.20999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.05</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>31.58</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.42</v>
+        <v>17.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.53</v>
+        <v>10.26</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5.13</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.84</v>
+        <v>38.46</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CC6" t="n">
         <v>7.42</v>
@@ -3205,10 +3205,10 @@
         <v>1.48</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH6" t="n">
         <v>1.3</v>
@@ -3217,7 +3217,7 @@
         <v>1.61</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CK6" t="n">
         <v>1.55</v>
@@ -3235,20 +3235,20 @@
         <v>1.43</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CR6" t="inlineStr"/>
       <c r="CS6" t="inlineStr"/>
       <c r="CT6" t="inlineStr"/>
       <c r="CU6" t="inlineStr"/>
       <c r="CV6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CX6" t="n">
         <v>1.79</v>
@@ -3263,55 +3263,55 @@
         <v>1.78</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="DE6" t="n">
         <v>0.03</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.42</v>
+        <v>84.62</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.03</v>
+        <v>3.95</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="DM6" t="n">
-        <v>31.4</v>
+        <v>31.51</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.79</v>
+        <v>10.85</v>
       </c>
       <c r="DQ6" t="n">
-        <v>7.66</v>
+        <v>7.95</v>
       </c>
       <c r="DR6" t="n">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="DS6" t="n">
         <v>0.13</v>
@@ -3323,28 +3323,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.92</v>
+        <v>47.23</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.34</v>
+        <v>10.28</v>
       </c>
       <c r="DY6" t="n">
         <v>7.1</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="EA6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="EB6" t="n">
         <v>1.11</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="7">
@@ -4551,13 +4551,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
         <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4644,49 +4644,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>73.79000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.53</v>
+        <v>31.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.84</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.16</v>
+        <v>4.65</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="AV10" t="n">
         <v>0.05</v>
@@ -4698,82 +4698,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45.95</v>
+        <v>44.85</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.58</v>
+        <v>10.35</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.26</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.32</v>
+        <v>8.65</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.31</v>
+        <v>9.18</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.62</v>
+        <v>4.47</v>
       </c>
       <c r="BR10" t="n">
-        <v>87.18000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>67.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>43.59</v>
+        <v>45</v>
       </c>
       <c r="BU10" t="n">
-        <v>25.64</v>
+        <v>27.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>46.15</v>
+        <v>45</v>
       </c>
       <c r="BY10" t="n">
         <v>2.02</v>
@@ -4782,13 +4782,13 @@
         <v>2.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB10" t="n">
         <v>3.64</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CD10" t="n">
         <v>5.26</v>
@@ -4812,16 +4812,16 @@
         <v>2.04</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="CO10" t="n">
         <v>1.38</v>
@@ -4830,7 +4830,7 @@
         <v>2.21</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="n">
@@ -4868,46 +4868,46 @@
         <v>4.14</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DH10" t="n">
-        <v>76.15000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.8</v>
+        <v>4.68</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="DM10" t="n">
-        <v>31.95</v>
+        <v>32.08</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.08</v>
+        <v>4.32</v>
       </c>
       <c r="DS10" t="n">
         <v>0.1</v>
@@ -4919,28 +4919,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>45.92</v>
+        <v>45.38</v>
       </c>
       <c r="DW10" t="n">
         <v>0.28</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.1</v>
+        <v>10.98</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.23</v>
+        <v>7.2</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="EA10" t="n">
-        <v>7.9</v>
+        <v>8.07</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="11">
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -6546,49 +6546,49 @@
         <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>80.68000000000001</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>4.05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="M15" t="n">
-        <v>34.95</v>
+        <v>39.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.79</v>
+        <v>6.7</v>
       </c>
       <c r="R15" t="n">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6600,28 +6600,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.68</v>
+        <v>47.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.95</v>
+        <v>11.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.63</v>
+        <v>7.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.79</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AF15" t="n">
         <v>0.11</v>
@@ -6705,67 +6705,67 @@
         <v>2.79</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.18</v>
+        <v>4.05</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.08</v>
+        <v>3.95</v>
       </c>
       <c r="BR15" t="n">
-        <v>89.47</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>65.79000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>44.74</v>
+        <v>46.15</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.05</v>
+        <v>23.08</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.89</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.11</v>
+        <v>41.03</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="BZ15" t="n">
         <v>3.42</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CB15" t="n">
         <v>3.92</v>
@@ -6780,10 +6780,10 @@
         <v>1.48</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH15" t="n">
         <v>1.31</v>
@@ -6792,28 +6792,28 @@
         <v>1.64</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CO15" t="n">
         <v>1.42</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ15" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
@@ -6854,43 +6854,43 @@
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DH15" t="n">
-        <v>77.23999999999999</v>
+        <v>79.97</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.39</v>
+        <v>3.31</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM15" t="n">
-        <v>32.18</v>
+        <v>34.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.52</v>
+        <v>11.43</v>
       </c>
       <c r="DQ15" t="n">
-        <v>6.79</v>
+        <v>6.74</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.32</v>
+        <v>4.41</v>
       </c>
       <c r="DS15" t="n">
         <v>0.02</v>
@@ -6902,28 +6902,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>42.9</v>
+        <v>43.75</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.56</v>
+        <v>10.9</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.42</v>
+        <v>7.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="EA15" t="n">
-        <v>9.26</v>
+        <v>9.69</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="16">
@@ -7328,13 +7328,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="n">
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
         <v>0.17</v>
@@ -7418,139 +7418,139 @@
         <v>2.87</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.45</v>
+        <v>77.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.73</v>
+        <v>3.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="AM17" t="n">
         <v>0.09</v>
       </c>
       <c r="AN17" t="n">
-        <v>32.55</v>
+        <v>32.7</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.45</v>
+        <v>10.91</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.36</v>
+        <v>6.65</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.73</v>
+        <v>4.96</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>48.91</v>
+        <v>48.57</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.73</v>
+        <v>11.65</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.27</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="BE17" t="n">
         <v>1.29</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.82</v>
+        <v>8.67</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="BN17" t="n">
         <v>1.11</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.16</v>
+        <v>4.07</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="BR17" t="n">
-        <v>84.44</v>
+        <v>84.78</v>
       </c>
       <c r="BS17" t="n">
-        <v>60</v>
+        <v>60.87</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.22</v>
+        <v>43.48</v>
       </c>
       <c r="BU17" t="n">
-        <v>24.44</v>
+        <v>23.91</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.11</v>
+        <v>10.87</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BX17" t="n">
-        <v>42.22</v>
+        <v>43.48</v>
       </c>
       <c r="BY17" t="n">
         <v>1.85</v>
@@ -7559,22 +7559,22 @@
         <v>1.86</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CG17" t="n">
         <v>2.49</v>
@@ -7586,16 +7586,16 @@
         <v>1.67</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN17" t="n">
         <v>1.74</v>
@@ -7607,17 +7607,17 @@
         <v>2.3</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="CR17" t="inlineStr"/>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="inlineStr"/>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CX17" t="n">
         <v>1.77</v>
@@ -7632,55 +7632,55 @@
         <v>1.79</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DH17" t="n">
-        <v>88.53</v>
+        <v>87.94</v>
       </c>
       <c r="DI17" t="n">
         <v>0.22</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.53</v>
+        <v>4.46</v>
       </c>
       <c r="DL17" t="n">
         <v>0.13</v>
       </c>
       <c r="DM17" t="n">
-        <v>39.13</v>
+        <v>39.07</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.11</v>
+        <v>11.32</v>
       </c>
       <c r="DQ17" t="n">
-        <v>6.33</v>
+        <v>6.48</v>
       </c>
       <c r="DR17" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="DS17" t="n">
         <v>0.15</v>
@@ -7692,28 +7692,28 @@
         <v>0.02</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.07</v>
+        <v>51.83</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.16</v>
+        <v>14.06</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.550000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="EA17" t="n">
-        <v>10.87</v>
+        <v>10.98</v>
       </c>
       <c r="EB17" t="n">
         <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
         <v>0.15</v>
@@ -1469,52 +1469,52 @@
         <v>2.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.68000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>33.89</v>
+        <v>33.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.949999999999999</v>
+        <v>10.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.11</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AV2" t="n">
         <v>0.05</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>44.95</v>
+        <v>45.55</v>
       </c>
       <c r="AZ2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BK2" t="n">
         <v>0.32</v>
       </c>
-      <c r="BA2" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.33</v>
-      </c>
       <c r="BL2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.95</v>
+        <v>4.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BR2" t="n">
-        <v>84.62</v>
+        <v>85</v>
       </c>
       <c r="BS2" t="n">
-        <v>61.54</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>41.03</v>
+        <v>40</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.08</v>
+        <v>22.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.26</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>38.46</v>
+        <v>37.5</v>
       </c>
       <c r="BY2" t="n">
         <v>2.09</v>
@@ -1610,31 +1610,31 @@
         <v>2.11</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.47</v>
+        <v>4.51</v>
       </c>
       <c r="CE2" t="n">
         <v>1.45</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CH2" t="n">
         <v>1.27</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CJ2" t="n">
         <v>2.07</v>
@@ -1646,10 +1646,10 @@
         <v>1.73</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CO2" t="n">
         <v>1.32</v>
@@ -1658,17 +1658,17 @@
         <v>2.2</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX2" t="n">
         <v>1.76</v>
@@ -1683,55 +1683,55 @@
         <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
         <v>1.85</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.13</v>
+        <v>83.7</v>
       </c>
       <c r="DI2" t="n">
         <v>0.15</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="DM2" t="n">
-        <v>38.56</v>
+        <v>38.38</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.9</v>
+        <v>12.15</v>
       </c>
       <c r="DQ2" t="n">
-        <v>5.31</v>
+        <v>5.45</v>
       </c>
       <c r="DR2" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="DS2" t="n">
         <v>0.1</v>
@@ -1743,28 +1743,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.67</v>
+        <v>49.85</v>
       </c>
       <c r="DW2" t="n">
         <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.61</v>
+        <v>12.48</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="EA2" t="n">
-        <v>9.59</v>
+        <v>9.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="3">
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
         <v>0.13</v>
@@ -1867,49 +1867,49 @@
         <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="AI3" t="n">
-        <v>89.68000000000001</v>
+        <v>89.91</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>35.74</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.32</v>
+        <v>12.04</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.45</v>
+        <v>5.52</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AV3" t="n">
         <v>0.09</v>
@@ -1921,82 +1921,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.5</v>
+        <v>50.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>11.87</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.050000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.56</v>
+        <v>9.52</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
         <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
         <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.38</v>
+        <v>4.26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.64</v>
+        <v>4.52</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.67</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.11</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>34.78</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>39.13</v>
       </c>
       <c r="BY3" t="n">
         <v>1.85</v>
@@ -2011,13 +2011,13 @@
         <v>3.4</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF3" t="n">
         <v>3.26</v>
@@ -2047,13 +2047,13 @@
         <v>1.61</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP3" t="n">
         <v>2.3</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="CR3" t="n">
         <v>1.68</v>
@@ -2064,10 +2064,10 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CX3" t="n">
         <v>1.78</v>
@@ -2082,55 +2082,55 @@
         <v>1.79</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="DE3" t="n">
         <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.8</v>
+        <v>90.89</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>39.89</v>
+        <v>39.68</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.87</v>
+        <v>11.74</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.6</v>
+        <v>6.63</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="DS3" t="n">
         <v>0.09</v>
@@ -2142,25 +2142,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.76</v>
+        <v>53.61</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.31</v>
+        <v>14.2</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.49</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>7.76</v>
+        <v>8</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="EC3" t="n">
         <v>2.35</v>
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
         <v>0.15</v>
@@ -2263,139 +2263,139 @@
         <v>3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AI4" t="n">
-        <v>82.58</v>
+        <v>84.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.21</v>
+        <v>37.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.16</v>
+        <v>10.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.16</v>
+        <v>7.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.53</v>
+        <v>49.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.32</v>
+        <v>11.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.42</v>
+        <v>7.35</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.42</v>
+        <v>10.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.949999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BN4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.18</v>
       </c>
-      <c r="BO4" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BP4" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.36</v>
+        <v>4.28</v>
       </c>
       <c r="BR4" t="n">
-        <v>89.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.79000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>17.95</v>
+        <v>17.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>48.72</v>
+        <v>47.5</v>
       </c>
       <c r="BY4" t="n">
         <v>2</v>
@@ -2404,16 +2404,16 @@
         <v>1.76</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="CE4" t="n">
         <v>1.5</v>
@@ -2434,10 +2434,10 @@
         <v>2.15</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM4" t="n">
         <v>2.02</v>
@@ -2462,7 +2462,7 @@
         <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CX4" t="n">
         <v>1.82</v>
@@ -2477,25 +2477,25 @@
         <v>1.79</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.45999999999999</v>
+        <v>90.25</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
@@ -2504,55 +2504,55 @@
         <v>3.18</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.15</v>
+        <v>5.08</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.59</v>
+        <v>40.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.59</v>
+        <v>11.62</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.23</v>
+        <v>6.55</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0.05</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.77</v>
+        <v>54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.87</v>
+        <v>12.75</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="EA4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="EB4" t="n">
         <v>1.44</v>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
         <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2658,139 +2658,139 @@
         <v>2.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.95</v>
+        <v>86.52</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>38.27</v>
+        <v>37.52</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.86</v>
+        <v>10.83</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.36</v>
+        <v>7.48</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.32</v>
+        <v>5.52</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.86</v>
+        <v>55.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.73</v>
+        <v>13.57</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.18</v>
+        <v>7.91</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BG5" t="n">
         <v>2.78</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.69</v>
+        <v>9.67</v>
       </c>
       <c r="BI5" t="n">
         <v>2.78</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>89.13</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.33</v>
+        <v>73.91</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.78</v>
+        <v>58.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>28.89</v>
+        <v>28.26</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.56</v>
+        <v>15.22</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.78</v>
+        <v>58.7</v>
       </c>
       <c r="BY5" t="n">
         <v>1.51</v>
@@ -2799,65 +2799,65 @@
         <v>1.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH5" t="n">
         <v>1.37</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
         <v>1.5</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM5" t="n">
         <v>2.18</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
         <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
@@ -2871,52 +2871,52 @@
         <v>1.31</v>
       </c>
       <c r="DC5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="DE5" t="n">
         <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
       <c r="DH5" t="n">
-        <v>92</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.84</v>
+        <v>5.76</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.06</v>
+        <v>39.65</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.69</v>
+        <v>11.66</v>
       </c>
       <c r="DQ5" t="n">
-        <v>6.96</v>
+        <v>7.02</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.67</v>
+        <v>4.78</v>
       </c>
       <c r="DS5" t="n">
         <v>0.31</v>
@@ -2928,28 +2928,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.86</v>
+        <v>57.54</v>
       </c>
       <c r="DW5" t="n">
         <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.98</v>
+        <v>15.85</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.31</v>
+        <v>10.24</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.67</v>
+        <v>5.61</v>
       </c>
       <c r="EA5" t="n">
-        <v>9.56</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="6">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
         <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
         <v>0.22</v>
@@ -3444,52 +3444,52 @@
         <v>2.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.95</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.05</v>
+        <v>33.3</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.95</v>
+        <v>5.04</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3501,82 +3501,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.64</v>
+        <v>53</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.14</v>
+        <v>10.39</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.27</v>
+        <v>6.48</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.09</v>
+        <v>8.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BO7" t="n">
         <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>89.13</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.89</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.22</v>
+        <v>43.48</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.89</v>
+        <v>28.26</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="BX7" t="n">
-        <v>51.11</v>
+        <v>52.17</v>
       </c>
       <c r="BY7" t="n">
         <v>1.92</v>
@@ -3585,22 +3585,22 @@
         <v>2.15</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CE7" t="n">
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CG7" t="n">
         <v>2.48</v>
@@ -3621,7 +3621,7 @@
         <v>2.03</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CN7" t="n">
         <v>1.52</v>
@@ -3633,7 +3633,7 @@
         <v>2.3</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CR7" t="n">
         <v>1.68</v>
@@ -3644,22 +3644,22 @@
       </c>
       <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX7" t="n">
         <v>1.84</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.86</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB7" t="n">
         <v>1.43</v>
@@ -3671,79 +3671,79 @@
         <v>4.36</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.27</v>
+        <v>81.53</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.45</v>
+        <v>33.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.31</v>
+        <v>10.26</v>
       </c>
       <c r="DQ7" t="n">
         <v>5.94</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.29</v>
+        <v>53.46</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.07</v>
+        <v>12.15</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.89</v>
+        <v>7.96</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="EA7" t="n">
-        <v>8.06</v>
+        <v>8.44</v>
       </c>
       <c r="EB7" t="n">
         <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="8">
@@ -3753,55 +3753,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
         <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="H8" t="n">
-        <v>87.68000000000001</v>
+        <v>87.75</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="K8" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>43.11</v>
+        <v>42.65</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>14.16</v>
+        <v>14.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.47</v>
+        <v>6.55</v>
       </c>
       <c r="R8" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
         <v>1.05</v>
@@ -3810,37 +3810,37 @@
         <v>0.95</v>
       </c>
       <c r="U8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.95</v>
+        <v>51.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.11</v>
+        <v>12.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.630000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.16</v>
+        <v>9.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3924,70 +3924,70 @@
         <v>2.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.15</v>
+        <v>9.07</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK8" t="n">
         <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.49</v>
+        <v>4.42</v>
       </c>
       <c r="BR8" t="n">
-        <v>79.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>58.97</v>
+        <v>60</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>32.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.08</v>
+        <v>22.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.46</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
         <v>2.25</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CA8" t="n">
         <v>3.17</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CC8" t="n">
         <v>4.42</v>
@@ -4011,10 +4011,10 @@
         <v>1.66</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL8" t="n">
         <v>2.03</v>
@@ -4023,16 +4023,16 @@
         <v>2.03</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO8" t="n">
         <v>1.45</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
       <c r="CR8" t="inlineStr"/>
       <c r="CS8" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
         <v>1.71</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CX8" t="n">
         <v>1.8</v>
@@ -4063,7 +4063,7 @@
         <v>2.45</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="DE8" t="n">
         <v>0.15</v>
@@ -4072,73 +4072,73 @@
         <v>1.82</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DH8" t="n">
-        <v>85.59</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.21</v>
+        <v>40.05</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.21</v>
+        <v>13.3</v>
       </c>
       <c r="DQ8" t="n">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="DR8" t="n">
-        <v>3.97</v>
+        <v>4.08</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.31</v>
+        <v>51.2</v>
       </c>
       <c r="DW8" t="n">
         <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.03</v>
+        <v>11.18</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.67</v>
+        <v>7.78</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="EA8" t="n">
-        <v>9.18</v>
+        <v>9.15</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -4148,94 +4148,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
         <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="F9" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>85.26000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="K9" t="n">
-        <v>4.37</v>
+        <v>4.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>37.84</v>
+        <v>36.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>12.95</v>
+        <v>13.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.84</v>
+        <v>5.25</v>
       </c>
       <c r="R9" t="n">
-        <v>3.89</v>
+        <v>4.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="V9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.53</v>
+        <v>45.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.79</v>
+        <v>12.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.789999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB9" t="n">
         <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.74</v>
+        <v>8.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AF9" t="n">
         <v>0.1</v>
@@ -4319,70 +4319,70 @@
         <v>3.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="BK9" t="n">
         <v>0.38</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.87</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>67.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>41.03</v>
+        <v>42.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>17.95</v>
+        <v>17.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.15</v>
+        <v>45</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC9" t="n">
         <v>5.14</v>
@@ -4391,7 +4391,7 @@
         <v>5.89</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF9" t="n">
         <v>3.45</v>
@@ -4406,7 +4406,7 @@
         <v>1.6</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CK9" t="n">
         <v>1.64</v>
@@ -4424,10 +4424,10 @@
         <v>1.45</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="CR9" t="n">
         <v>1.72</v>
@@ -4442,10 +4442,10 @@
         <v>2.08</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CX9" t="n">
         <v>1.81</v>
@@ -4460,55 +4460,55 @@
         <v>1.75</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DD9" t="n">
-        <v>5.01</v>
+        <v>4.95</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.87</v>
+        <v>78.97</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>30.46</v>
+        <v>29.88</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="DQ9" t="n">
-        <v>5.85</v>
+        <v>6.02</v>
       </c>
       <c r="DR9" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="DS9" t="n">
         <v>0.1</v>
@@ -4520,28 +4520,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.75</v>
+        <v>43.58</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.82</v>
+        <v>7.8</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="EA9" t="n">
-        <v>8.1</v>
+        <v>8.35</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="10">
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
         <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
         <v>0.1</v>
@@ -5040,139 +5040,139 @@
         <v>3.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>53.79</v>
+        <v>54.55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.37</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.37</v>
+        <v>14.55</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.37</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>36.89</v>
+        <v>37.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.21</v>
+        <v>10.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.16</v>
+        <v>7.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.59</v>
+        <v>4.55</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>56.41</v>
+        <v>57.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>30.77</v>
+        <v>32.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>48.72</v>
+        <v>47.5</v>
       </c>
       <c r="BY11" t="n">
         <v>3.46</v>
@@ -5184,13 +5184,13 @@
         <v>3.46</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CC11" t="n">
-        <v>6.94</v>
+        <v>6.82</v>
       </c>
       <c r="CD11" t="n">
-        <v>8.15</v>
+        <v>7.8</v>
       </c>
       <c r="CE11" t="n">
         <v>1.46</v>
@@ -5202,7 +5202,7 @@
         <v>2.53</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI11" t="n">
         <v>1.64</v>
@@ -5214,10 +5214,10 @@
         <v>1.58</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN11" t="n">
         <v>1.68</v>
@@ -5263,52 +5263,52 @@
         <v>4.31</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DH11" t="n">
-        <v>69.13</v>
+        <v>69.12</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="DM11" t="n">
-        <v>30.69</v>
+        <v>30.75</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="DQ11" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.21</v>
+        <v>5.28</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
@@ -5317,25 +5317,25 @@
         <v>43.15</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.51</v>
+        <v>10.6</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.43</v>
+        <v>7.42</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="EA11" t="n">
-        <v>8.869999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="EC11" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="12">
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5438,79 +5438,79 @@
         <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
-        <v>80.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.79</v>
+        <v>31.15</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.84</v>
+        <v>10.95</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.42</v>
+        <v>7.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" t="n">
         <v>0.05</v>
       </c>
       <c r="AY12" t="n">
-        <v>53.11</v>
+        <v>52.95</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.84</v>
+        <v>12.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.789999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BF12" t="n">
         <v>2.05</v>
@@ -5519,22 +5519,22 @@
         <v>2.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI12" t="n">
         <v>2.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN12" t="n">
         <v>1.1</v>
@@ -5543,31 +5543,31 @@
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.26</v>
+        <v>4.28</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.18000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>61.54</v>
+        <v>62.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>32.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>20.51</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>41.03</v>
+        <v>40</v>
       </c>
       <c r="BY12" t="n">
         <v>2.39</v>
@@ -5579,22 +5579,22 @@
         <v>3.09</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CC12" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="CD12" t="n">
         <v>4.08</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>4.3</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CH12" t="n">
         <v>1.26</v>
@@ -5609,35 +5609,35 @@
         <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN12" t="n">
         <v>1.68</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
         <v>2.28</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CY12" t="n">
         <v>1.89</v>
@@ -5652,82 +5652,82 @@
         <v>1.47</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="DE12" t="n">
         <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.69</v>
+        <v>84.7</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.51</v>
+        <v>4.6</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.9</v>
+        <v>33.02</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.2</v>
+        <v>6.48</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
       <c r="DS12" t="n">
         <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0.02</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.95</v>
+        <v>52.88</v>
       </c>
       <c r="DW12" t="n">
         <v>0.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.49</v>
+        <v>12.62</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.640000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.85</v>
       </c>
       <c r="EA12" t="n">
-        <v>9.49</v>
+        <v>9.65</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
         <v>2.38</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
         <v>24</v>
@@ -5752,82 +5752,82 @@
         <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>94.09</v>
+        <v>94.17</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="K13" t="n">
-        <v>5.78</v>
+        <v>5.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>44.35</v>
+        <v>44.12</v>
       </c>
       <c r="N13" t="n">
         <v>1.17</v>
       </c>
       <c r="O13" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>12.39</v>
+        <v>12.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.91</v>
+        <v>6.88</v>
       </c>
       <c r="R13" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="T13" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>59.91</v>
+        <v>59.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.26</v>
+        <v>17.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.74</v>
+        <v>11.96</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.22</v>
+        <v>7.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>0.12</v>
@@ -5911,58 +5911,58 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.039999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="BR13" t="n">
-        <v>89.36</v>
+        <v>89.58</v>
       </c>
       <c r="BS13" t="n">
-        <v>70.20999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT13" t="n">
-        <v>40.43</v>
+        <v>41.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.4</v>
+        <v>22.92</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.77</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.51</v>
+        <v>8.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>51.06</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>1.71</v>
@@ -5989,10 +5989,10 @@
         <v>3.06</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI13" t="n">
         <v>1.66</v>
@@ -6004,13 +6004,13 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM13" t="n">
         <v>2</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO13" t="n">
         <v>1.33</v>
@@ -6019,7 +6019,7 @@
         <v>2.15</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CR13" t="n">
         <v>1.68</v>
@@ -6033,7 +6033,7 @@
         <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX13" t="n">
         <v>1.77</v>
@@ -6045,91 +6045,91 @@
         <v>1.91</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB13" t="n">
         <v>1.38</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="DE13" t="n">
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="DH13" t="n">
-        <v>92.28</v>
+        <v>92.36</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.02</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM13" t="n">
-        <v>42</v>
+        <v>41.93</v>
       </c>
       <c r="DN13" t="n">
         <v>1.21</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>10.94</v>
       </c>
       <c r="DQ13" t="n">
-        <v>6.92</v>
+        <v>6.9</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.62</v>
+        <v>56.54</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.7</v>
+        <v>15.85</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.47</v>
+        <v>10.6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="EA13" t="n">
-        <v>7.83</v>
+        <v>7.92</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="14">
@@ -6139,94 +6139,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
         <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F14" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="H14" t="n">
-        <v>84.91</v>
+        <v>87.13</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J14" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
-        <v>5.45</v>
+        <v>5.52</v>
       </c>
       <c r="L14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="M14" t="n">
-        <v>40.32</v>
+        <v>42.61</v>
       </c>
       <c r="N14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="P14" t="n">
-        <v>10.32</v>
+        <v>10.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.55</v>
+        <v>5.74</v>
       </c>
       <c r="R14" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="S14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="U14" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="W14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="X14" t="n">
-        <v>56.27</v>
+        <v>56.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.27</v>
+        <v>13.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.640000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.64</v>
+        <v>4.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>7.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AF14" t="n">
         <v>0.13</v>
@@ -6310,64 +6310,64 @@
         <v>2.74</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BH14" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BO14" t="n">
         <v>1.11</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.11</v>
+        <v>91.3</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.11</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>44.44</v>
+        <v>45.65</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>21.74</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.11</v>
+        <v>10.87</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="BX14" t="n">
-        <v>51.11</v>
+        <v>52.17</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CA14" t="n">
         <v>3.4</v>
@@ -6385,19 +6385,19 @@
         <v>1.45</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CH14" t="n">
         <v>1.33</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK14" t="n">
         <v>1.63</v>
@@ -6409,26 +6409,26 @@
         <v>2.05</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX14" t="n">
         <v>1.83</v>
@@ -6443,58 +6443,58 @@
         <v>1.76</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DE14" t="n">
         <v>0.2</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.64</v>
+        <v>84.78</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="DL14" t="n">
         <v>0.24</v>
       </c>
       <c r="DM14" t="n">
-        <v>37.18</v>
+        <v>38.39</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.11</v>
+        <v>10.08</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.07</v>
+        <v>7.13</v>
       </c>
       <c r="DR14" t="n">
         <v>4.84</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT14" t="n">
         <v>0.22</v>
@@ -6503,25 +6503,25 @@
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.51</v>
+        <v>53.58</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.62</v>
+        <v>11.76</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.71</v>
+        <v>7.78</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.91</v>
+        <v>3.98</v>
       </c>
       <c r="EA14" t="n">
-        <v>8.220000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="EC14" t="n">
         <v>2.55</v>
@@ -6933,40 +6933,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="G16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="H16" t="n">
-        <v>84.53</v>
+        <v>85.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="M16" t="n">
-        <v>35.16</v>
+        <v>35.55</v>
       </c>
       <c r="N16" t="n">
         <v>1.05</v>
@@ -6975,19 +6975,19 @@
         <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>10.37</v>
+        <v>10.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.63</v>
+        <v>6.25</v>
       </c>
       <c r="R16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="U16" t="n">
         <v>0.05</v>
@@ -6999,28 +6999,28 @@
         <v>0.05</v>
       </c>
       <c r="X16" t="n">
-        <v>50.26</v>
+        <v>50.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>10.58</v>
+        <v>10.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.84</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
         <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AF16" t="n">
         <v>0.05</v>
@@ -7104,64 +7104,64 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.03</v>
+        <v>9.98</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BN16" t="n">
         <v>1.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BR16" t="n">
-        <v>89.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS16" t="n">
-        <v>56.41</v>
+        <v>57.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>48.72</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>20.51</v>
+        <v>20</v>
       </c>
       <c r="BV16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BX16" t="n">
-        <v>38.46</v>
+        <v>37.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="CA16" t="n">
         <v>3.28</v>
@@ -7179,10 +7179,10 @@
         <v>1.5</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CH16" t="n">
         <v>1.29</v>
@@ -7194,25 +7194,25 @@
         <v>2.18</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP16" t="n">
         <v>2.31</v>
       </c>
       <c r="CQ16" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="CR16" t="inlineStr"/>
       <c r="CS16" t="inlineStr"/>
@@ -7234,7 +7234,7 @@
         <v>1.92</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB16" t="n">
         <v>1.41</v>
@@ -7249,28 +7249,28 @@
         <v>0.1</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="DG16" t="n">
         <v>2.1</v>
       </c>
       <c r="DH16" t="n">
-        <v>80.8</v>
+        <v>81.38</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="DL16" t="n">
         <v>0.28</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.1</v>
+        <v>33.35</v>
       </c>
       <c r="DN16" t="n">
         <v>1.02</v>
@@ -7279,46 +7279,46 @@
         <v>2</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.03</v>
+        <v>9.9</v>
       </c>
       <c r="DQ16" t="n">
-        <v>5.56</v>
+        <v>5.88</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="DS16" t="n">
         <v>0.05</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DU16" t="n">
         <v>0.02</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.41</v>
+        <v>47.65</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="DX16" t="n">
-        <v>9.720000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.03</v>
+        <v>7.08</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="EA16" t="n">
-        <v>8.23</v>
+        <v>8.5</v>
       </c>
       <c r="EB16" t="n">
         <v>1.06</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="17">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
         <v>0.13</v>
@@ -7813,139 +7813,139 @@
         <v>3.04</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AI18" t="n">
-        <v>76.29000000000001</v>
+        <v>77.23</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.43</v>
+        <v>33.18</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.81</v>
+        <v>10.68</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.9</v>
+        <v>8.32</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.52</v>
+        <v>6.82</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AV18" t="n">
         <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX18" t="n">
         <v>0.05</v>
       </c>
       <c r="AY18" t="n">
-        <v>47.86</v>
+        <v>48.09</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.24</v>
+        <v>10.36</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.05</v>
+        <v>7.14</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.52</v>
+        <v>9.77</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.59</v>
+        <v>9.51</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL18" t="n">
         <v>0.73</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.98</v>
+        <v>4.91</v>
       </c>
       <c r="BR18" t="n">
-        <v>86.36</v>
+        <v>86.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>61.36</v>
+        <v>62.22</v>
       </c>
       <c r="BT18" t="n">
-        <v>47.73</v>
+        <v>46.67</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.18</v>
+        <v>17.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.45</v>
+        <v>46.67</v>
       </c>
       <c r="BY18" t="n">
         <v>2.18</v>
@@ -7954,16 +7954,16 @@
         <v>2.31</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.89</v>
+        <v>4.79</v>
       </c>
       <c r="CE18" t="n">
         <v>1.46</v>
@@ -7978,7 +7978,7 @@
         <v>1.32</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ18" t="n">
         <v>2.02</v>
@@ -7993,7 +7993,7 @@
         <v>2.3</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO18" t="n">
         <v>1.37</v>
@@ -8002,7 +8002,7 @@
         <v>2.21</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="CR18" t="inlineStr"/>
       <c r="CS18" t="inlineStr"/>
@@ -8016,95 +8016,95 @@
       </c>
       <c r="CX18" t="inlineStr"/>
       <c r="CY18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ18" t="inlineStr"/>
       <c r="DA18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC18" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.34</v>
+        <v>79.73</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.5</v>
+        <v>39.24</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.39</v>
+        <v>11.31</v>
       </c>
       <c r="DQ18" t="n">
-        <v>7.65</v>
+        <v>7.87</v>
       </c>
       <c r="DR18" t="n">
-        <v>5.64</v>
+        <v>5.8</v>
       </c>
       <c r="DS18" t="n">
         <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU18" t="n">
         <v>0.02</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.64</v>
+        <v>49.71</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX18" t="n">
         <v>12.55</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="EA18" t="n">
-        <v>9.52</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="EB18" t="n">
         <v>1.38</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="19">
@@ -8114,10 +8114,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
         <v>20</v>
@@ -8126,82 +8126,82 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H19" t="n">
-        <v>87.63</v>
+        <v>88.3</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="J19" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="K19" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="M19" t="n">
-        <v>48.16</v>
+        <v>48.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
-        <v>11.11</v>
+        <v>10.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.79</v>
+        <v>5.9</v>
       </c>
       <c r="R19" t="n">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="S19" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="W19" t="n">
         <v>0.05</v>
       </c>
       <c r="X19" t="n">
-        <v>49.05</v>
+        <v>48.55</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.37</v>
+        <v>12.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.630000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AF19" t="n">
         <v>0.05</v>
@@ -8285,28 +8285,28 @@
         <v>2.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.720000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BO19" t="n">
         <v>0.92</v>
@@ -8315,40 +8315,40 @@
         <v>4.92</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="BR19" t="n">
-        <v>84.62</v>
+        <v>85</v>
       </c>
       <c r="BS19" t="n">
-        <v>61.54</v>
+        <v>62.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>43.59</v>
+        <v>45</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.08</v>
+        <v>22.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>10.26</v>
+        <v>10</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BX19" t="n">
-        <v>53.85</v>
+        <v>55</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CC19" t="n">
         <v>4.64</v>
@@ -8360,22 +8360,22 @@
         <v>1.52</v>
       </c>
       <c r="CF19" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CH19" t="n">
         <v>1.28</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ19" t="n">
         <v>2.18</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL19" t="n">
         <v>2.12</v>
@@ -8390,20 +8390,20 @@
         <v>1.46</v>
       </c>
       <c r="CP19" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CQ19" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="CR19" t="inlineStr"/>
       <c r="CS19" t="inlineStr"/>
       <c r="CT19" t="inlineStr"/>
       <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CW19" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CX19" t="n">
         <v>1.86</v>
@@ -8427,79 +8427,79 @@
         <v>4.5</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="DG19" t="n">
         <v>2.15</v>
       </c>
       <c r="DH19" t="n">
-        <v>82.92</v>
+        <v>83.38</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.59</v>
+        <v>41.82</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.77</v>
+        <v>11.65</v>
       </c>
       <c r="DQ19" t="n">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
       <c r="DR19" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="DS19" t="n">
         <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU19" t="n">
         <v>0.02</v>
       </c>
       <c r="DV19" t="n">
-        <v>47.74</v>
+        <v>47.52</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.74</v>
+        <v>11.72</v>
       </c>
       <c r="DY19" t="n">
         <v>7.8</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="EA19" t="n">
-        <v>9.26</v>
+        <v>9.57</v>
       </c>
       <c r="EB19" t="n">
         <v>1.32</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="20">
@@ -8509,58 +8509,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="H20" t="n">
-        <v>86.3</v>
+        <v>86.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J20" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="K20" t="n">
-        <v>5.78</v>
+        <v>5.62</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="M20" t="n">
-        <v>39.52</v>
+        <v>39.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="P20" t="n">
-        <v>11.48</v>
+        <v>11.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.91</v>
+        <v>6.46</v>
       </c>
       <c r="R20" t="n">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="S20" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="T20" t="n">
         <v>1.17</v>
@@ -8575,28 +8575,28 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.78</v>
+        <v>53.33</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.87</v>
+        <v>14.79</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.3</v>
+        <v>10.21</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.39</v>
+        <v>11.79</v>
       </c>
       <c r="AD20" t="n">
         <v>1.54</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="AF20" t="n">
         <v>0.12</v>
@@ -8680,70 +8680,70 @@
         <v>3.25</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.43</v>
+        <v>9.35</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BL20" t="n">
         <v>0.6</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BN20" t="n">
         <v>1.15</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BP20" t="n">
         <v>4.15</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="BR20" t="n">
-        <v>85.11</v>
+        <v>85.42</v>
       </c>
       <c r="BS20" t="n">
-        <v>65.95999999999999</v>
+        <v>64.58</v>
       </c>
       <c r="BT20" t="n">
-        <v>42.55</v>
+        <v>41.67</v>
       </c>
       <c r="BU20" t="n">
-        <v>12.77</v>
+        <v>12.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.38</v>
+        <v>6.25</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.26</v>
+        <v>4.17</v>
       </c>
       <c r="BX20" t="n">
-        <v>51.06</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CA20" t="n">
         <v>3.21</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CC20" t="n">
         <v>3.6</v>
@@ -8770,13 +8770,13 @@
         <v>2.07</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL20" t="n">
         <v>1.94</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN20" t="n">
         <v>1.73</v>
@@ -8785,7 +8785,7 @@
         <v>1.42</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ20" t="n">
         <v>4.2</v>
@@ -8798,13 +8798,13 @@
         <v>1.78</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CY20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ20" t="n">
         <v>1.87</v>
@@ -8813,55 +8813,55 @@
         <v>1.81</v>
       </c>
       <c r="DB20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DH20" t="n">
-        <v>79.51000000000001</v>
+        <v>79.62</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM20" t="n">
-        <v>34.21</v>
+        <v>34.31</v>
       </c>
       <c r="DN20" t="n">
         <v>1.19</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DP20" t="n">
         <v>11.4</v>
       </c>
       <c r="DQ20" t="n">
-        <v>6.45</v>
+        <v>6.71</v>
       </c>
       <c r="DR20" t="n">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="DS20" t="n">
         <v>0.17</v>
@@ -8873,28 +8873,28 @@
         <v>0.02</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.66</v>
+        <v>47.56</v>
       </c>
       <c r="DW20" t="n">
         <v>0.21</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="DY20" t="n">
         <v>8.32</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="EA20" t="n">
-        <v>9.98</v>
+        <v>10.2</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC20" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="21">
@@ -8904,94 +8904,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="F21" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="G21" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="H21" t="n">
-        <v>84.72</v>
+        <v>85.11</v>
       </c>
       <c r="I21" t="n">
         <v>0.11</v>
       </c>
       <c r="J21" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="M21" t="n">
-        <v>39.39</v>
+        <v>39.42</v>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O21" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="P21" t="n">
-        <v>13.28</v>
+        <v>13.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="R21" t="n">
-        <v>3.61</v>
+        <v>3.95</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="U21" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="V21" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="W21" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="X21" t="n">
-        <v>52.56</v>
+        <v>52.42</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.17</v>
+        <v>14.21</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.78</v>
+        <v>5.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9075,61 +9075,61 @@
         <v>2.55</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.66</v>
+        <v>8.69</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BL21" t="n">
         <v>0.82</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.37</v>
+        <v>4.38</v>
       </c>
       <c r="BR21" t="n">
-        <v>92.11</v>
+        <v>92.31</v>
       </c>
       <c r="BS21" t="n">
-        <v>71.05</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>44.74</v>
+        <v>43.59</v>
       </c>
       <c r="BU21" t="n">
-        <v>28.95</v>
+        <v>28.21</v>
       </c>
       <c r="BV21" t="n">
-        <v>7.89</v>
+        <v>7.69</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>55.26</v>
+        <v>53.85</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BZ21" t="n">
         <v>3.35</v>
@@ -9150,7 +9150,7 @@
         <v>1.48</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CG21" t="n">
         <v>2.49</v>
@@ -9162,19 +9162,19 @@
         <v>1.64</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CK21" t="n">
         <v>1.61</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM21" t="n">
         <v>1.96</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO21" t="n">
         <v>1.43</v>
@@ -9183,7 +9183,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="CR21" t="n">
         <v>1.72</v>
@@ -9194,10 +9194,10 @@
       </c>
       <c r="CU21" t="inlineStr"/>
       <c r="CV21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CX21" t="n">
         <v>1.85</v>
@@ -9212,88 +9212,88 @@
         <v>1.85</v>
       </c>
       <c r="DB21" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DD21" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DH21" t="n">
-        <v>75.58</v>
+        <v>76</v>
       </c>
       <c r="DI21" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="DM21" t="n">
-        <v>31.63</v>
+        <v>31.85</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DO21" t="n">
         <v>1.9</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.69</v>
+        <v>12.79</v>
       </c>
       <c r="DQ21" t="n">
-        <v>5.5</v>
+        <v>5.69</v>
       </c>
       <c r="DR21" t="n">
-        <v>4.84</v>
+        <v>4.98</v>
       </c>
       <c r="DS21" t="n">
         <v>0.13</v>
       </c>
       <c r="DT21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU21" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.77</v>
+        <v>45.87</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.5</v>
+        <v>11.59</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.58</v>
+        <v>7.64</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="EA21" t="n">
-        <v>6.63</v>
+        <v>6.77</v>
       </c>
       <c r="EB21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="n">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
         <v>0.13</v>
@@ -7813,139 +7813,139 @@
         <v>3.04</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AI18" t="n">
-        <v>77.23</v>
+        <v>75.48</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.23</v>
+        <v>3.39</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.18</v>
+        <v>32.39</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.68</v>
+        <v>10.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>8.32</v>
+        <v>8.26</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.82</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW18" t="n">
         <v>0.09</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.09</v>
+        <v>48.35</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.36</v>
+        <v>10.35</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.77</v>
+        <v>9.57</v>
       </c>
       <c r="BE18" t="n">
         <v>1.12</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.51</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="BQ18" t="n">
         <v>4.91</v>
       </c>
       <c r="BR18" t="n">
-        <v>86.67</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>62.22</v>
+        <v>63.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>46.67</v>
+        <v>47.83</v>
       </c>
       <c r="BU18" t="n">
-        <v>17.78</v>
+        <v>17.39</v>
       </c>
       <c r="BV18" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BX18" t="n">
-        <v>46.67</v>
+        <v>45.65</v>
       </c>
       <c r="BY18" t="n">
         <v>2.18</v>
@@ -7960,7 +7960,7 @@
         <v>3.4</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="CD18" t="n">
         <v>4.79</v>
@@ -7969,7 +7969,7 @@
         <v>1.46</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CG18" t="n">
         <v>2.57</v>
@@ -7984,13 +7984,13 @@
         <v>2.02</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN18" t="n">
         <v>1.78</v>
@@ -8002,7 +8002,7 @@
         <v>2.21</v>
       </c>
       <c r="CQ18" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="CR18" t="inlineStr"/>
       <c r="CS18" t="inlineStr"/>
@@ -8032,46 +8032,46 @@
         <v>4.01</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DH18" t="n">
-        <v>79.73</v>
+        <v>78.8</v>
       </c>
       <c r="DI18" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.24</v>
+        <v>38.72</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.31</v>
+        <v>11.22</v>
       </c>
       <c r="DQ18" t="n">
-        <v>7.87</v>
+        <v>7.84</v>
       </c>
       <c r="DR18" t="n">
-        <v>5.8</v>
+        <v>5.92</v>
       </c>
       <c r="DS18" t="n">
         <v>0.13</v>
@@ -8083,28 +8083,28 @@
         <v>0.02</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.71</v>
+        <v>49.8</v>
       </c>
       <c r="DW18" t="n">
         <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.55</v>
+        <v>12.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="EA18" t="n">
-        <v>9.640000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="EB18" t="n">
         <v>1.38</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="19">
@@ -8904,94 +8904,94 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
         <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="n">
-        <v>85.11</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
         <v>2.95</v>
       </c>
       <c r="K21" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="L21" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="M21" t="n">
-        <v>39.42</v>
+        <v>38.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O21" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>13.47</v>
+        <v>13.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.89</v>
+        <v>5.95</v>
       </c>
       <c r="R21" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="S21" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T21" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="W21" t="n">
         <v>0.05</v>
       </c>
       <c r="X21" t="n">
-        <v>52.42</v>
+        <v>52.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>14.21</v>
+        <v>14.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>9.84</v>
+        <v>9.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>4.37</v>
+        <v>4.25</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.16</v>
+        <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -9075,67 +9075,67 @@
         <v>2.55</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="BH21" t="n">
-        <v>8.69</v>
+        <v>8.75</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="BP21" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="BR21" t="n">
-        <v>92.31</v>
+        <v>92.5</v>
       </c>
       <c r="BS21" t="n">
-        <v>71.79000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>43.59</v>
+        <v>45</v>
       </c>
       <c r="BU21" t="n">
-        <v>28.21</v>
+        <v>27.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
       <c r="BW21" t="n">
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>53.85</v>
+        <v>52.5</v>
       </c>
       <c r="BY21" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="BZ21" t="n">
         <v>3.35</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CB21" t="n">
         <v>3.59</v>
@@ -9150,7 +9150,7 @@
         <v>1.48</v>
       </c>
       <c r="CF21" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CG21" t="n">
         <v>2.49</v>
@@ -9159,22 +9159,22 @@
         <v>1.3</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ21" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CK21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM21" t="n">
         <v>1.96</v>
       </c>
       <c r="CN21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CO21" t="n">
         <v>1.43</v>
@@ -9183,7 +9183,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ21" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="CR21" t="n">
         <v>1.72</v>
@@ -9197,7 +9197,7 @@
         <v>1.67</v>
       </c>
       <c r="CW21" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CX21" t="n">
         <v>1.85</v>
@@ -9221,16 +9221,16 @@
         <v>4.31</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DH21" t="n">
-        <v>76</v>
+        <v>75.22</v>
       </c>
       <c r="DI21" t="n">
         <v>0.08</v>
@@ -9239,31 +9239,31 @@
         <v>3</v>
       </c>
       <c r="DK21" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM21" t="n">
-        <v>31.85</v>
+        <v>31.48</v>
       </c>
       <c r="DN21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DO21" t="n">
         <v>1.9</v>
       </c>
       <c r="DP21" t="n">
-        <v>12.79</v>
+        <v>12.65</v>
       </c>
       <c r="DQ21" t="n">
-        <v>5.69</v>
+        <v>5.72</v>
       </c>
       <c r="DR21" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT21" t="n">
         <v>0.1</v>
@@ -9272,28 +9272,28 @@
         <v>0.02</v>
       </c>
       <c r="DV21" t="n">
-        <v>45.87</v>
+        <v>45.88</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DX21" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="DY21" t="n">
-        <v>7.64</v>
+        <v>7.7</v>
       </c>
       <c r="DZ21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="EA21" t="n">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="EB21" t="n">
         <v>1.24</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -2173,94 +2173,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>96</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>0.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>43.8</v>
+        <v>42.67</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="P4" t="n">
-        <v>12.95</v>
+        <v>12.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.35</v>
+        <v>5.62</v>
       </c>
       <c r="R4" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="T4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="U4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="W4" t="n">
         <v>0.1</v>
       </c>
       <c r="X4" t="n">
-        <v>58.75</v>
+        <v>57.71</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.35</v>
+        <v>14.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.75</v>
+        <v>8.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="AC4" t="n">
         <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2344,64 +2344,64 @@
         <v>2.65</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>72.5</v>
+        <v>70.73</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.5</v>
+        <v>46.34</v>
       </c>
       <c r="BU4" t="n">
-        <v>17.5</v>
+        <v>17.07</v>
       </c>
       <c r="BV4" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>47.5</v>
+        <v>46.34</v>
       </c>
       <c r="BY4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CA4" t="n">
         <v>3.22</v>
@@ -2419,7 +2419,7 @@
         <v>1.5</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CG4" t="n">
         <v>2.43</v>
@@ -2431,16 +2431,16 @@
         <v>1.64</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CK4" t="n">
         <v>1.56</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN4" t="n">
         <v>1.61</v>
@@ -2489,46 +2489,46 @@
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.25</v>
+        <v>88.39</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.08</v>
+        <v>5.02</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.62</v>
+        <v>11.49</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT4" t="n">
         <v>0.2</v>
@@ -2537,28 +2537,28 @@
         <v>0.05</v>
       </c>
       <c r="DV4" t="n">
-        <v>54</v>
+        <v>53.58</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.75</v>
+        <v>12.68</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="EA4" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="n">
         <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
         <v>0.22</v>
@@ -3447,49 +3447,49 @@
         <v>0.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.56999999999999</v>
+        <v>77.58</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="AM7" t="n">
         <v>0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.3</v>
+        <v>33.04</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.43</v>
+        <v>9.08</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.65</v>
+        <v>5.79</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.04</v>
+        <v>5.33</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3501,82 +3501,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53</v>
+        <v>52.75</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.04</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.39</v>
+        <v>10.46</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.48</v>
+        <v>6.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.83</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP7" t="n">
         <v>3.26</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="BR7" t="n">
-        <v>89.13</v>
+        <v>89.36</v>
       </c>
       <c r="BS7" t="n">
-        <v>69.56999999999999</v>
+        <v>68.09</v>
       </c>
       <c r="BT7" t="n">
-        <v>43.48</v>
+        <v>42.55</v>
       </c>
       <c r="BU7" t="n">
-        <v>28.26</v>
+        <v>27.66</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.17</v>
+        <v>51.06</v>
       </c>
       <c r="BY7" t="n">
         <v>1.92</v>
@@ -3588,13 +3588,13 @@
         <v>3.29</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CE7" t="n">
         <v>1.48</v>
@@ -3609,10 +3609,10 @@
         <v>1.29</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CK7" t="n">
         <v>1.59</v>
@@ -3624,7 +3624,7 @@
         <v>1.87</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO7" t="n">
         <v>1.37</v>
@@ -3674,43 +3674,43 @@
         <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.53</v>
+        <v>80.47</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="DL7" t="n">
         <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.56</v>
+        <v>33.43</v>
       </c>
       <c r="DN7" t="n">
         <v>1.17</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.26</v>
+        <v>10.06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.46</v>
+        <v>4.62</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.46</v>
+        <v>53.32</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
@@ -3731,19 +3731,19 @@
         <v>12.15</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.96</v>
+        <v>7.93</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="EA7" t="n">
-        <v>8.44</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="8">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>20</v>
@@ -5357,82 +5357,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="H12" t="n">
-        <v>88.75</v>
+        <v>86.14</v>
       </c>
       <c r="I12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>5.55</v>
+        <v>5.43</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="M12" t="n">
-        <v>34.9</v>
+        <v>34.24</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>10.05</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.05</v>
+        <v>5.29</v>
       </c>
       <c r="R12" t="n">
-        <v>4.7</v>
+        <v>4.81</v>
       </c>
       <c r="S12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.8</v>
+        <v>52.81</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.15</v>
+        <v>11.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AF12" t="n">
         <v>0.05</v>
@@ -5516,70 +5516,70 @@
         <v>2.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.5</v>
+        <v>87.8</v>
       </c>
       <c r="BS12" t="n">
-        <v>62.5</v>
+        <v>60.98</v>
       </c>
       <c r="BT12" t="n">
-        <v>32.5</v>
+        <v>31.71</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>19.51</v>
       </c>
       <c r="BV12" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BX12" t="n">
-        <v>40</v>
+        <v>39.02</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CA12" t="n">
         <v>3.09</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CC12" t="n">
         <v>3.98</v>
@@ -5600,13 +5600,13 @@
         <v>1.26</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL12" t="n">
         <v>2.02</v>
@@ -5618,23 +5618,23 @@
         <v>1.68</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX12" t="n">
         <v>1.8</v>
@@ -5649,58 +5649,58 @@
         <v>1.8</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC12" t="n">
         <v>2.46</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="DE12" t="n">
         <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.7</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.02</v>
+        <v>32.73</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="DO12" t="n">
         <v>2.15</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.5</v>
+        <v>10.27</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.48</v>
+        <v>6.56</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
         <v>0.15</v>
@@ -5712,25 +5712,25 @@
         <v>52.88</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.62</v>
+        <v>12.59</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="EA12" t="n">
-        <v>9.65</v>
+        <v>10.15</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="13">
@@ -5740,13 +5740,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5833,49 +5833,49 @@
         <v>0.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AI13" t="n">
-        <v>90.54000000000001</v>
+        <v>90.88</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.04</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.42</v>
+        <v>5.52</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.75</v>
+        <v>41.52</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.67</v>
+        <v>9.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.92</v>
+        <v>7.24</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>1.04</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AV13" t="n">
         <v>0.12</v>
@@ -5887,82 +5887,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.46</v>
+        <v>53.64</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.21</v>
+        <v>14.28</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
       <c r="BC13" t="n">
         <v>4.96</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.42</v>
+        <v>9.32</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.02</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.98</v>
+        <v>4.06</v>
       </c>
       <c r="BR13" t="n">
-        <v>89.58</v>
+        <v>89.8</v>
       </c>
       <c r="BS13" t="n">
-        <v>70.83</v>
+        <v>69.39</v>
       </c>
       <c r="BT13" t="n">
-        <v>41.67</v>
+        <v>40.82</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.92</v>
+        <v>22.45</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>12.24</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>8.16</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>48.98</v>
       </c>
       <c r="BY13" t="n">
         <v>1.71</v>
@@ -5974,40 +5974,40 @@
         <v>3.32</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC13" t="n">
         <v>2.49</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CH13" t="n">
         <v>1.3</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN13" t="n">
         <v>1.58</v>
@@ -6016,10 +6016,10 @@
         <v>1.33</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CR13" t="n">
         <v>1.68</v>
@@ -6030,10 +6030,10 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CX13" t="n">
         <v>1.77</v>
@@ -6048,55 +6048,55 @@
         <v>1.8</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="DE13" t="n">
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="DH13" t="n">
-        <v>92.36</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.02</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.58</v>
+        <v>5.63</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="DM13" t="n">
-        <v>41.93</v>
+        <v>42.79</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.94</v>
+        <v>10.84</v>
       </c>
       <c r="DQ13" t="n">
-        <v>6.9</v>
+        <v>7.06</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="DS13" t="n">
         <v>0.18</v>
@@ -6108,28 +6108,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.54</v>
+        <v>56.57</v>
       </c>
       <c r="DW13" t="n">
         <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.85</v>
+        <v>15.86</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.6</v>
+        <v>10.61</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="EA13" t="n">
-        <v>7.92</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="14">
@@ -6139,94 +6139,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="H14" t="n">
-        <v>87.13</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0.04</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="K14" t="n">
-        <v>5.52</v>
+        <v>5.38</v>
       </c>
       <c r="L14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="M14" t="n">
-        <v>42.61</v>
+        <v>42.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="O14" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="P14" t="n">
-        <v>10.26</v>
+        <v>10.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="R14" t="n">
-        <v>3.91</v>
+        <v>4.12</v>
       </c>
       <c r="S14" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="V14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="n">
         <v>0.04</v>
       </c>
       <c r="X14" t="n">
-        <v>56.3</v>
+        <v>55.71</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.48</v>
+        <v>13.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.74</v>
+        <v>8.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.74</v>
+        <v>4.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.65</v>
+        <v>8.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="AF14" t="n">
         <v>0.13</v>
@@ -6310,70 +6310,70 @@
         <v>2.74</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.109999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BJ14" t="n">
         <v>0.7</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BO14" t="n">
         <v>1.11</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.72</v>
+        <v>4.79</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.3</v>
+        <v>91.48999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.73999999999999</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>45.65</v>
+        <v>44.68</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.74</v>
+        <v>21.28</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.87</v>
+        <v>10.64</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.17</v>
+        <v>51.06</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="CA14" t="n">
         <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC14" t="n">
         <v>3.72</v>
@@ -6385,25 +6385,25 @@
         <v>1.45</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CH14" t="n">
         <v>1.33</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK14" t="n">
         <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM14" t="n">
         <v>2.05</v>
@@ -6418,113 +6418,113 @@
         <v>2.16</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CX14" t="n">
         <v>1.81</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>1.83</v>
       </c>
       <c r="CY14" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DA14" t="n">
         <v>1.76</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.78</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="DL14" t="n">
         <v>0.24</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.39</v>
+        <v>38.55</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.08</v>
+        <v>10.19</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.13</v>
+        <v>7.11</v>
       </c>
       <c r="DR14" t="n">
-        <v>4.84</v>
+        <v>4.93</v>
       </c>
       <c r="DS14" t="n">
         <v>0.23</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU14" t="n">
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.58</v>
+        <v>53.34</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.76</v>
+        <v>11.7</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.78</v>
+        <v>7.77</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="EA14" t="n">
-        <v>8.52</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -8509,13 +8509,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
         <v>0.08</v>
@@ -8602,52 +8602,52 @@
         <v>0.12</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH20" t="n">
         <v>1.92</v>
       </c>
       <c r="AI20" t="n">
-        <v>73</v>
+        <v>70.52</v>
       </c>
       <c r="AJ20" t="n">
         <v>0.12</v>
       </c>
       <c r="AK20" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>29.12</v>
+        <v>28.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.33</v>
+        <v>10.92</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.96</v>
+        <v>7.44</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.67</v>
+        <v>7.56</v>
       </c>
       <c r="AT20" t="n">
         <v>1.12</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AW20" t="n">
         <v>0.12</v>
@@ -8656,82 +8656,82 @@
         <v>0.04</v>
       </c>
       <c r="AY20" t="n">
-        <v>41.79</v>
+        <v>42.64</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.789999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.42</v>
+        <v>6.88</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BO20" t="n">
         <v>1.06</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="BR20" t="n">
-        <v>85.42</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS20" t="n">
-        <v>64.58</v>
+        <v>63.27</v>
       </c>
       <c r="BT20" t="n">
-        <v>41.67</v>
+        <v>40.82</v>
       </c>
       <c r="BU20" t="n">
-        <v>12.5</v>
+        <v>12.24</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BX20" t="n">
-        <v>50</v>
+        <v>48.98</v>
       </c>
       <c r="BY20" t="n">
         <v>2.07</v>
@@ -8746,7 +8746,7 @@
         <v>3.43</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="CD20" t="n">
         <v>4.62</v>
@@ -8755,7 +8755,7 @@
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CG20" t="n">
         <v>2.5</v>
@@ -8764,7 +8764,7 @@
         <v>1.31</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ20" t="n">
         <v>2.07</v>
@@ -8816,7 +8816,7 @@
         <v>1.39</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DD20" t="n">
         <v>4.1</v>
@@ -8825,46 +8825,46 @@
         <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DH20" t="n">
-        <v>79.62</v>
+        <v>78.22</v>
       </c>
       <c r="DI20" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="DL20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DP20" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="DQ20" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="DR20" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="DS20" t="n">
         <v>0.16</v>
-      </c>
-      <c r="DM20" t="n">
-        <v>34.31</v>
-      </c>
-      <c r="DN20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DO20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DP20" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="DQ20" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="DR20" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="DS20" t="n">
-        <v>0.17</v>
       </c>
       <c r="DT20" t="n">
         <v>0.14</v>
@@ -8873,28 +8873,28 @@
         <v>0.02</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.56</v>
+        <v>47.88</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.29</v>
+        <v>12.43</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.32</v>
+        <v>8.51</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="EA20" t="n">
-        <v>10.2</v>
+        <v>10.37</v>
       </c>
       <c r="EB20" t="n">
         <v>1.3</v>
       </c>
       <c r="EC20" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
         <v>0.13</v>
@@ -1864,139 +1864,139 @@
         <v>2.35</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AI3" t="n">
-        <v>89.91</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>35.74</v>
+        <v>35.79</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.04</v>
+        <v>11.92</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.52</v>
+        <v>6.04</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.35</v>
+        <v>50.04</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.87</v>
+        <v>11.58</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.52</v>
+        <v>8.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL3" t="n">
         <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="BP3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>87.23</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="BV3" t="n">
         <v>4.26</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>86.95999999999999</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>71.73999999999999</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>34.78</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>4.35</v>
-      </c>
       <c r="BW3" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="BX3" t="n">
-        <v>39.13</v>
+        <v>38.3</v>
       </c>
       <c r="BY3" t="n">
         <v>1.85</v>
@@ -2005,34 +2005,34 @@
         <v>1.94</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.87</v>
+        <v>3.02</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.07</v>
+        <v>3.32</v>
       </c>
       <c r="CE3" t="n">
         <v>1.48</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CH3" t="n">
         <v>1.3</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CK3" t="n">
         <v>1.57</v>
@@ -2041,7 +2041,7 @@
         <v>2.03</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN3" t="n">
         <v>1.61</v>
@@ -2050,10 +2050,10 @@
         <v>1.39</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CR3" t="n">
         <v>1.68</v>
@@ -2064,106 +2064,106 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CX3" t="n">
         <v>1.78</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.9</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.89</v>
+        <v>91.06</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="DM3" t="n">
-        <v>39.68</v>
+        <v>39.62</v>
       </c>
       <c r="DN3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.74</v>
+        <v>11.68</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.74</v>
+        <v>5.02</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.61</v>
+        <v>53.38</v>
       </c>
       <c r="DW3" t="n">
         <v>0.19</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.390000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="EA3" t="n">
-        <v>8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,7 +2185,7 @@
         <v>0.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
         <v>2.38</v>
@@ -2197,7 +2197,7 @@
         <v>0.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="K4" t="n">
         <v>5.38</v>
@@ -2260,7 +2260,7 @@
         <v>1.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2489,7 +2489,7 @@
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="DG4" t="n">
         <v>2.41</v>
@@ -2501,7 +2501,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="DK4" t="n">
         <v>5.02</v>
@@ -2558,7 +2558,7 @@
         <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="5">
@@ -2568,94 +2568,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="G5" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="H5" t="n">
-        <v>96.83</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>-0.04</v>
       </c>
       <c r="J5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="K5" t="n">
-        <v>6.26</v>
+        <v>6.38</v>
       </c>
       <c r="L5" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="M5" t="n">
-        <v>41.78</v>
+        <v>42.96</v>
       </c>
       <c r="N5" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="O5" t="n">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="P5" t="n">
-        <v>12.48</v>
+        <v>12.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.57</v>
+        <v>6.71</v>
       </c>
       <c r="R5" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="S5" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="V5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.78</v>
+        <v>59.67</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.13</v>
+        <v>18.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.52</v>
+        <v>11.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.61</v>
+        <v>6.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.83</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0.13</v>
@@ -2739,58 +2739,58 @@
         <v>2.74</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.67</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.8</v>
+        <v>4.68</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.13</v>
+        <v>89.36</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.91</v>
+        <v>72.34</v>
       </c>
       <c r="BT5" t="n">
-        <v>58.7</v>
+        <v>57.45</v>
       </c>
       <c r="BU5" t="n">
-        <v>28.26</v>
+        <v>27.66</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.22</v>
+        <v>14.89</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.7</v>
+        <v>57.45</v>
       </c>
       <c r="BY5" t="n">
         <v>1.51</v>
@@ -2802,7 +2802,7 @@
         <v>3.68</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CC5" t="n">
         <v>2.2</v>
@@ -2814,13 +2814,13 @@
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI5" t="n">
         <v>1.75</v>
@@ -2829,7 +2829,7 @@
         <v>2.02</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL5" t="n">
         <v>1.93</v>
@@ -2847,7 +2847,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CZ5" t="inlineStr"/>
       <c r="DA5" t="n">
@@ -2871,85 +2871,85 @@
         <v>1.31</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.76</v>
+        <v>5.83</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="DM5" t="n">
-        <v>39.65</v>
+        <v>40.3</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.66</v>
+        <v>11.6</v>
       </c>
       <c r="DQ5" t="n">
-        <v>7.02</v>
+        <v>7.09</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.78</v>
+        <v>4.81</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.54</v>
+        <v>57.53</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.85</v>
+        <v>15.87</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.24</v>
+        <v>10.32</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.61</v>
+        <v>5.55</v>
       </c>
       <c r="EA5" t="n">
-        <v>9.869999999999999</v>
+        <v>10</v>
       </c>
       <c r="EB5" t="n">
         <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="6">
@@ -5893,10 +5893,10 @@
         <v>0.24</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.28</v>
+        <v>14.32</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.32</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BC13" t="n">
         <v>4.96</v>
@@ -6114,10 +6114,10 @@
         <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.86</v>
+        <v>15.88</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.61</v>
+        <v>10.63</v>
       </c>
       <c r="DZ13" t="n">
         <v>5.24</v>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1774,94 +1774,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
         <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="H3" t="n">
-        <v>91.87</v>
+        <v>91.75</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J3" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="K3" t="n">
-        <v>6.48</v>
+        <v>6.38</v>
       </c>
       <c r="L3" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>43.61</v>
+        <v>42.67</v>
       </c>
       <c r="N3" t="n">
         <v>0.96</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="P3" t="n">
-        <v>11.43</v>
+        <v>11.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.26</v>
+        <v>6.33</v>
       </c>
       <c r="R3" t="n">
-        <v>3.96</v>
+        <v>4.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.87</v>
+        <v>56.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.52</v>
+        <v>16.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.48</v>
+        <v>10.12</v>
       </c>
       <c r="AB3" t="n">
         <v>6.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.48</v>
+        <v>8.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1903,7 +1903,7 @@
         <v>7.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.04</v>
+        <v>6.12</v>
       </c>
       <c r="AT3" t="n">
         <v>0.92</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.04</v>
+        <v>50</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.21</v>
@@ -1936,7 +1936,7 @@
         <v>3.42</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BE3" t="n">
         <v>1.24</v>
@@ -1945,70 +1945,70 @@
         <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.57</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.23</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>70.20999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT3" t="n">
-        <v>34.04</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.51</v>
+        <v>8.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.26</v>
+        <v>4.17</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BX3" t="n">
-        <v>38.3</v>
+        <v>39.58</v>
       </c>
       <c r="BY3" t="n">
         <v>1.85</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CA3" t="n">
         <v>3.31</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC3" t="n">
         <v>3.02</v>
@@ -2020,19 +2020,19 @@
         <v>1.48</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CG3" t="n">
         <v>2.48</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI3" t="n">
         <v>1.65</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK3" t="n">
         <v>1.57</v>
@@ -2044,16 +2044,16 @@
         <v>2.02</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO3" t="n">
         <v>1.39</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="CR3" t="n">
         <v>1.68</v>
@@ -2064,10 +2064,10 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CX3" t="n">
         <v>1.78</v>
@@ -2085,52 +2085,52 @@
         <v>1.45</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
       <c r="DE3" t="n">
         <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.06</v>
+        <v>91.02</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.3</v>
+        <v>5.28</v>
       </c>
       <c r="DL3" t="n">
         <v>0.19</v>
       </c>
       <c r="DM3" t="n">
-        <v>39.62</v>
+        <v>39.23</v>
       </c>
       <c r="DN3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.68</v>
+        <v>11.73</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.68</v>
+        <v>6.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.02</v>
+        <v>5.18</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.38</v>
+        <v>53.25</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DX3" t="n">
-        <v>14</v>
+        <v>13.88</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="EA3" t="n">
-        <v>8.130000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="EB3" t="n">
         <v>1.5</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
         <v>0.14</v>
@@ -2269,133 +2269,133 @@
         <v>2.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>84.5</v>
+        <v>83.38</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.65</v>
+        <v>4.43</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.6</v>
+        <v>36.81</v>
       </c>
       <c r="AO4" t="n">
         <v>0.95</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.3</v>
+        <v>10.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.75</v>
+        <v>7.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.25</v>
+        <v>4.43</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>49.25</v>
+        <v>48.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.15</v>
+        <v>11.05</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.35</v>
+        <v>7.38</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>10.05</v>
+        <v>10.62</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.23999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.73</v>
+        <v>69.05</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.34</v>
+        <v>45.24</v>
       </c>
       <c r="BU4" t="n">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.34</v>
+        <v>45.24</v>
       </c>
       <c r="BY4" t="n">
         <v>1.99</v>
@@ -2407,13 +2407,13 @@
         <v>3.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CE4" t="n">
         <v>1.5</v>
@@ -2437,7 +2437,7 @@
         <v>1.56</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM4" t="n">
         <v>2.03</v>
@@ -2452,17 +2452,17 @@
         <v>2.36</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CX4" t="n">
         <v>1.82</v>
@@ -2492,70 +2492,70 @@
         <v>1.98</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.39</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.02</v>
+        <v>4.9</v>
       </c>
       <c r="DL4" t="n">
         <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.2</v>
+        <v>39.74</v>
       </c>
       <c r="DN4" t="n">
         <v>1.22</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.66</v>
+        <v>6.74</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.88</v>
+        <v>3.97</v>
       </c>
       <c r="DS4" t="n">
         <v>0.24</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU4" t="n">
         <v>0.05</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.58</v>
+        <v>53.11</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.68</v>
+        <v>12.6</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.97</v>
+        <v>7.98</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="EA4" t="n">
-        <v>9.51</v>
+        <v>9.81</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
         <v>2.93</v>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2595,7 +2595,7 @@
         <v>2.46</v>
       </c>
       <c r="K5" t="n">
-        <v>6.38</v>
+        <v>6.42</v>
       </c>
       <c r="L5" t="n">
         <v>0.67</v>
@@ -2613,7 +2613,7 @@
         <v>12.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
       <c r="R5" t="n">
         <v>4.12</v>
@@ -2634,163 +2634,163 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.67</v>
+        <v>59.71</v>
       </c>
       <c r="Y5" t="n">
         <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.08</v>
+        <v>18.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.62</v>
+        <v>11.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>12.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE5" t="n">
         <v>2.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.52</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.26</v>
+        <v>5.38</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>37.52</v>
+        <v>37.21</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.83</v>
+        <v>10.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.48</v>
+        <v>7.88</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.52</v>
+        <v>5.62</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.3</v>
+        <v>54.88</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.57</v>
+        <v>13.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.91</v>
+        <v>8.08</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.36</v>
+        <v>87.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.34</v>
+        <v>70.83</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.45</v>
+        <v>56.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.66</v>
+        <v>27.08</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.89</v>
+        <v>14.58</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.51</v>
+        <v>8.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.45</v>
+        <v>56.25</v>
       </c>
       <c r="BY5" t="n">
         <v>1.51</v>
@@ -2799,16 +2799,16 @@
         <v>1.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CE5" t="n">
         <v>1.4</v>
@@ -2823,10 +2823,10 @@
         <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK5" t="n">
         <v>1.51</v>
@@ -2847,28 +2847,28 @@
         <v>2.03</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ5" t="inlineStr"/>
       <c r="DA5" t="n">
         <v>1.82</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC5" t="n">
         <v>1.98</v>
@@ -2880,13 +2880,13 @@
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.27</v>
+        <v>92.25</v>
       </c>
       <c r="DI5" t="n">
         <v>0.04</v>
@@ -2895,28 +2895,28 @@
         <v>3.04</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.3</v>
+        <v>40.08</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.6</v>
+        <v>11.54</v>
       </c>
       <c r="DQ5" t="n">
-        <v>7.09</v>
+        <v>7.32</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.81</v>
+        <v>4.87</v>
       </c>
       <c r="DS5" t="n">
         <v>0.3</v>
@@ -2928,28 +2928,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.53</v>
+        <v>57.29</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.87</v>
+        <v>15.88</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.32</v>
+        <v>10.38</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="EB5" t="n">
         <v>1.68</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="6">
@@ -3354,94 +3354,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
         <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="H7" t="n">
-        <v>83.48</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J7" t="n">
         <v>3.04</v>
       </c>
       <c r="K7" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>33.83</v>
+        <v>34.58</v>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>11.09</v>
+        <v>11.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.22</v>
+        <v>6.38</v>
       </c>
       <c r="R7" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="T7" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.91</v>
+        <v>54.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.43</v>
+        <v>9.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.039999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3525,70 +3525,70 @@
         <v>2.21</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="BR7" t="n">
-        <v>89.36</v>
+        <v>87.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.09</v>
+        <v>66.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.55</v>
+        <v>41.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.66</v>
+        <v>27.08</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.51</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BX7" t="n">
-        <v>51.06</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CA7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CB7" t="n">
         <v>3.29</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.3</v>
       </c>
       <c r="CC7" t="n">
         <v>3.21</v>
@@ -3618,10 +3618,10 @@
         <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CN7" t="n">
         <v>1.53</v>
@@ -3647,7 +3647,7 @@
         <v>1.76</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX7" t="n">
         <v>1.84</v>
@@ -3668,49 +3668,49 @@
         <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="DE7" t="n">
         <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.47</v>
+        <v>81.31</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.43</v>
+        <v>33.81</v>
       </c>
       <c r="DN7" t="n">
         <v>1.17</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.06</v>
+        <v>10.1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3722,28 +3722,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.32</v>
+        <v>53.58</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.15</v>
+        <v>12.23</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.93</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="EA7" t="n">
-        <v>8.890000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="EB7" t="n">
         <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5438,52 +5438,52 @@
         <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AH12" t="n">
         <v>1.95</v>
       </c>
       <c r="AI12" t="n">
-        <v>80.65000000000001</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.15</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AQ12" t="n">
         <v>10.95</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.7</v>
+        <v>3.81</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW12" t="n">
         <v>0.1</v>
@@ -5492,82 +5492,82 @@
         <v>0.05</v>
       </c>
       <c r="AY12" t="n">
-        <v>52.95</v>
+        <v>53.48</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.15</v>
+        <v>12.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.75</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.15</v>
+        <v>9.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.34</v>
+        <v>9.26</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.8</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>60.98</v>
+        <v>61.9</v>
       </c>
       <c r="BT12" t="n">
-        <v>31.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>19.51</v>
+        <v>19.05</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="BX12" t="n">
-        <v>39.02</v>
+        <v>38.1</v>
       </c>
       <c r="BY12" t="n">
         <v>2.38</v>
@@ -5582,19 +5582,19 @@
         <v>3.23</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CH12" t="n">
         <v>1.26</v>
@@ -5609,7 +5609,7 @@
         <v>1.55</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM12" t="n">
         <v>2.12</v>
@@ -5624,7 +5624,7 @@
         <v>2.27</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
         <v>1.71</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX12" t="n">
         <v>1.8</v>
@@ -5652,85 +5652,85 @@
         <v>1.46</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="DE12" t="n">
         <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.45999999999999</v>
+        <v>83.22</v>
       </c>
       <c r="DI12" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.73</v>
+        <v>33.12</v>
       </c>
       <c r="DN12" t="n">
         <v>0.88</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.27</v>
+        <v>10.28</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0.02</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.88</v>
+        <v>53.14</v>
       </c>
       <c r="DW12" t="n">
         <v>0.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.59</v>
+        <v>12.66</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.81</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="EA12" t="n">
-        <v>10.15</v>
+        <v>10.38</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5740,94 +5740,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F13" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H13" t="n">
-        <v>94.17</v>
+        <v>93.8</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.33</v>
+        <v>3.24</v>
       </c>
       <c r="K13" t="n">
-        <v>5.75</v>
+        <v>5.68</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="M13" t="n">
-        <v>44.12</v>
+        <v>43.96</v>
       </c>
       <c r="N13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="P13" t="n">
-        <v>12.21</v>
+        <v>12.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.88</v>
+        <v>6.96</v>
       </c>
       <c r="R13" t="n">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="S13" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>59.62</v>
+        <v>59.44</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.5</v>
+        <v>17.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.96</v>
+        <v>11.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.54</v>
+        <v>5.68</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.42</v>
+        <v>7.68</v>
       </c>
       <c r="AD13" t="n">
         <v>1.81</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AF13" t="n">
         <v>0.12</v>
@@ -5911,64 +5911,64 @@
         <v>2.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.039999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BP13" t="n">
         <v>3.94</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.06</v>
+        <v>4.14</v>
       </c>
       <c r="BR13" t="n">
-        <v>89.8</v>
+        <v>88</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.39</v>
+        <v>68</v>
       </c>
       <c r="BT13" t="n">
-        <v>40.82</v>
+        <v>40</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.45</v>
+        <v>22</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.24</v>
+        <v>12</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.16</v>
+        <v>8</v>
       </c>
       <c r="BX13" t="n">
-        <v>48.98</v>
+        <v>48</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="CA13" t="n">
         <v>3.32</v>
@@ -5986,28 +5986,28 @@
         <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CH13" t="n">
         <v>1.3</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK13" t="n">
         <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN13" t="n">
         <v>1.58</v>
@@ -6019,7 +6019,7 @@
         <v>2.14</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CR13" t="n">
         <v>1.68</v>
@@ -6030,16 +6030,16 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX13" t="n">
         <v>1.77</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ13" t="n">
         <v>1.91</v>
@@ -6051,52 +6051,52 @@
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="DE13" t="n">
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DH13" t="n">
-        <v>92.48999999999999</v>
+        <v>92.34</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.02</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.79</v>
+        <v>42.74</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.84</v>
+        <v>10.96</v>
       </c>
       <c r="DQ13" t="n">
-        <v>7.06</v>
+        <v>7.1</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.67</v>
+        <v>4.76</v>
       </c>
       <c r="DS13" t="n">
         <v>0.18</v>
@@ -6108,28 +6108,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.57</v>
+        <v>56.54</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.88</v>
+        <v>15.84</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.63</v>
+        <v>10.52</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.24</v>
+        <v>5.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>8.390000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="EB13" t="n">
         <v>1.68</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="14">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
         <v>0.25</v>
@@ -6229,49 +6229,49 @@
         <v>2.46</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AI14" t="n">
-        <v>82.43000000000001</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>34.17</v>
+        <v>34.38</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.91</v>
+        <v>9.75</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.52</v>
+        <v>8.75</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.78</v>
+        <v>5.71</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AU14" t="n">
         <v>1.17</v>
@@ -6286,82 +6286,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.87</v>
+        <v>50.92</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.04</v>
+        <v>10.17</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.83</v>
+        <v>6.88</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.390000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="BG14" t="n">
         <v>2.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.130000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="BI14" t="n">
         <v>2.4</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK14" t="n">
         <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.79</v>
+        <v>4.71</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.48999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>70.20999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT14" t="n">
-        <v>44.68</v>
+        <v>43.75</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.28</v>
+        <v>20.83</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.64</v>
+        <v>10.42</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BX14" t="n">
-        <v>51.06</v>
+        <v>52.08</v>
       </c>
       <c r="BY14" t="n">
         <v>1.82</v>
@@ -6373,13 +6373,13 @@
         <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC14" t="n">
         <v>3.72</v>
       </c>
       <c r="CD14" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CE14" t="n">
         <v>1.45</v>
@@ -6415,20 +6415,20 @@
         <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX14" t="n">
         <v>1.81</v>
@@ -6446,52 +6446,52 @@
         <v>1.36</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.40000000000001</v>
+        <v>84.42</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.55</v>
+        <v>38.57</v>
       </c>
       <c r="DN14" t="n">
         <v>1.32</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.19</v>
+        <v>10.1</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.11</v>
+        <v>7.25</v>
       </c>
       <c r="DR14" t="n">
-        <v>4.93</v>
+        <v>4.92</v>
       </c>
       <c r="DS14" t="n">
         <v>0.23</v>
@@ -6503,28 +6503,28 @@
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.34</v>
+        <v>53.32</v>
       </c>
       <c r="DW14" t="n">
         <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.7</v>
+        <v>11.73</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.77</v>
+        <v>7.78</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="EA14" t="n">
-        <v>8.720000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="15">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
         <v>25</v>
@@ -8521,82 +8521,82 @@
         <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>86.25</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>0.08</v>
       </c>
       <c r="J20" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="K20" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="L20" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="M20" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="N20" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="O20" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="P20" t="n">
-        <v>11.46</v>
+        <v>11.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.46</v>
+        <v>6.56</v>
       </c>
       <c r="R20" t="n">
-        <v>4.21</v>
+        <v>4.28</v>
       </c>
       <c r="S20" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="U20" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="V20" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>53.33</v>
+        <v>52.64</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.79</v>
+        <v>14.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.21</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.79</v>
+        <v>11.56</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="AF20" t="n">
         <v>0.12</v>
@@ -8680,70 +8680,70 @@
         <v>3.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.33</v>
+        <v>9.26</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>4.12</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.76</v>
+        <v>4.7</v>
       </c>
       <c r="BR20" t="n">
-        <v>85.70999999999999</v>
+        <v>86</v>
       </c>
       <c r="BS20" t="n">
-        <v>63.27</v>
+        <v>64</v>
       </c>
       <c r="BT20" t="n">
-        <v>40.82</v>
+        <v>42</v>
       </c>
       <c r="BU20" t="n">
-        <v>12.24</v>
+        <v>12</v>
       </c>
       <c r="BV20" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BX20" t="n">
-        <v>48.98</v>
+        <v>48</v>
       </c>
       <c r="BY20" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CA20" t="n">
         <v>3.21</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CC20" t="n">
         <v>3.63</v>
@@ -8761,13 +8761,13 @@
         <v>2.5</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI20" t="n">
         <v>1.7</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK20" t="n">
         <v>1.55</v>
@@ -8779,23 +8779,23 @@
         <v>2.24</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP20" t="n">
         <v>2.26</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CR20" t="inlineStr"/>
       <c r="CS20" t="inlineStr"/>
       <c r="CT20" t="inlineStr"/>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CW20" t="n">
         <v>2.04</v>
@@ -8819,76 +8819,76 @@
         <v>2.26</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="DE20" t="n">
         <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="DH20" t="n">
-        <v>78.22</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="DI20" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.88</v>
+        <v>4.8</v>
       </c>
       <c r="DL20" t="n">
         <v>0.18</v>
       </c>
       <c r="DM20" t="n">
-        <v>34.04</v>
+        <v>34</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DP20" t="n">
         <v>11.18</v>
       </c>
       <c r="DQ20" t="n">
-        <v>6.96</v>
+        <v>7</v>
       </c>
       <c r="DR20" t="n">
         <v>5.92</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU20" t="n">
         <v>0.02</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.88</v>
+        <v>47.64</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.43</v>
+        <v>12.34</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.51</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="EA20" t="n">
-        <v>10.37</v>
+        <v>10.28</v>
       </c>
       <c r="EB20" t="n">
         <v>1.3</v>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
         <v>21</v>
@@ -2185,82 +2185,82 @@
         <v>0.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>92.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="I4" t="n">
         <v>0.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.43</v>
+        <v>3.32</v>
       </c>
       <c r="K4" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="L4" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>42.67</v>
+        <v>42.86</v>
       </c>
       <c r="N4" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="O4" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="P4" t="n">
-        <v>12.62</v>
+        <v>12.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.62</v>
+        <v>5.55</v>
       </c>
       <c r="R4" t="n">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="S4" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="T4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="X4" t="n">
-        <v>57.71</v>
+        <v>57.82</v>
       </c>
       <c r="Y4" t="n">
         <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.14</v>
+        <v>14.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.57</v>
+        <v>8.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2344,70 +2344,70 @@
         <v>2.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.789999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BO4" t="n">
         <v>1.14</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.12</v>
+        <v>4.21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.09999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.05</v>
+        <v>69.77</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.24</v>
+        <v>46.51</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>16.28</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.24</v>
+        <v>46.51</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CA4" t="n">
         <v>3.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CC4" t="n">
         <v>3.5</v>
@@ -2419,7 +2419,7 @@
         <v>1.5</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CG4" t="n">
         <v>2.43</v>
@@ -2443,7 +2443,7 @@
         <v>2.03</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO4" t="n">
         <v>1.44</v>
@@ -2452,17 +2452,17 @@
         <v>2.36</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CX4" t="n">
         <v>1.82</v>
@@ -2474,7 +2474,7 @@
         <v>1.87</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB4" t="n">
         <v>1.42</v>
@@ -2483,52 +2483,52 @@
         <v>2.33</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.73999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.74</v>
+        <v>39.91</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.48</v>
+        <v>11.26</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT4" t="n">
         <v>0.19</v>
@@ -2537,28 +2537,28 @@
         <v>0.05</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.11</v>
+        <v>53.28</v>
       </c>
       <c r="DW4" t="n">
         <v>0.26</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.98</v>
+        <v>8.09</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="EA4" t="n">
-        <v>9.81</v>
+        <v>9.93</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
         <v>0.21</v>
@@ -3444,52 +3444,52 @@
         <v>2.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AI7" t="n">
-        <v>77.58</v>
+        <v>77</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.79</v>
+        <v>3.68</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.04</v>
+        <v>33.08</v>
       </c>
       <c r="AO7" t="n">
         <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.08</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.79</v>
+        <v>5.76</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.33</v>
+        <v>5.52</v>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3501,82 +3501,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.75</v>
+        <v>52.24</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.46</v>
+        <v>10.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.710000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="BE7" t="n">
         <v>1.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="BR7" t="n">
-        <v>87.5</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.67</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.08</v>
+        <v>26.53</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>8.16</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>51.02</v>
       </c>
       <c r="BY7" t="n">
         <v>1.94</v>
@@ -3588,19 +3588,19 @@
         <v>3.28</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CC7" t="n">
         <v>3.21</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CE7" t="n">
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CG7" t="n">
         <v>2.48</v>
@@ -3612,7 +3612,7 @@
         <v>1.66</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CK7" t="n">
         <v>1.59</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW7" t="n">
         <v>2.07</v>
@@ -3668,49 +3668,49 @@
         <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.31</v>
+        <v>80.94</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.15</v>
+        <v>4.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DM7" t="n">
         <v>33.81</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.1</v>
+        <v>10.06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6.09</v>
+        <v>6.06</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.66</v>
+        <v>4.78</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3722,28 +3722,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.58</v>
+        <v>53.31</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.23</v>
+        <v>12.16</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.039999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="EA7" t="n">
-        <v>9.19</v>
+        <v>9.41</v>
       </c>
       <c r="EB7" t="n">
         <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" t="n">
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5438,136 +5438,136 @@
         <v>0.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="n">
         <v>1.95</v>
       </c>
       <c r="AI12" t="n">
-        <v>80.29000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>31.68</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.95</v>
+        <v>10.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.1</v>
+        <v>7.82</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.81</v>
+        <v>4.32</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="AV12" t="n">
         <v>0.14</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0.05</v>
       </c>
       <c r="AY12" t="n">
-        <v>53.48</v>
+        <v>52.86</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.67</v>
+        <v>9.82</v>
       </c>
       <c r="BE12" t="n">
         <v>1.27</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.26</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BO12" t="n">
         <v>0.98</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.09999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="BS12" t="n">
-        <v>61.9</v>
+        <v>62.79</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>34.88</v>
       </c>
       <c r="BU12" t="n">
-        <v>19.05</v>
+        <v>18.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>38.1</v>
+        <v>39.53</v>
       </c>
       <c r="BY12" t="n">
         <v>2.38</v>
@@ -5576,22 +5576,22 @@
         <v>2.21</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.97</v>
+        <v>4.06</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.07</v>
+        <v>4.26</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CG12" t="n">
         <v>2.4</v>
@@ -5609,7 +5609,7 @@
         <v>1.55</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM12" t="n">
         <v>2.12</v>
@@ -5624,7 +5624,7 @@
         <v>2.27</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
@@ -5634,7 +5634,7 @@
         <v>1.71</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX12" t="n">
         <v>1.8</v>
@@ -5655,49 +5655,49 @@
         <v>2.45</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.22</v>
+        <v>82.77</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.12</v>
+        <v>32.93</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.28</v>
+        <v>10.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.7</v>
+        <v>6.58</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.31</v>
+        <v>4.56</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5706,31 +5706,31 @@
         <v>0.14</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.14</v>
+        <v>52.84</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.66</v>
+        <v>12.65</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.81</v>
+        <v>3.84</v>
       </c>
       <c r="EA12" t="n">
-        <v>10.38</v>
+        <v>10.45</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="13">
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
         <v>25</v>
@@ -8521,82 +8521,82 @@
         <v>0.08</v>
       </c>
       <c r="F20" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="H20" t="n">
-        <v>85.40000000000001</v>
+        <v>86.73</v>
       </c>
       <c r="I20" t="n">
         <v>0.08</v>
       </c>
       <c r="J20" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="M20" t="n">
-        <v>39.2</v>
+        <v>40.69</v>
       </c>
       <c r="N20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="P20" t="n">
-        <v>11.44</v>
+        <v>11.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.56</v>
+        <v>6.62</v>
       </c>
       <c r="R20" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="T20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="U20" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="V20" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>52.64</v>
+        <v>52.92</v>
       </c>
       <c r="Y20" t="n">
         <v>0.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.52</v>
+        <v>14.58</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.880000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.64</v>
+        <v>4.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.56</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AF20" t="n">
         <v>0.12</v>
@@ -8680,70 +8680,70 @@
         <v>3.2</v>
       </c>
       <c r="BG20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>2.2</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>86</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>64</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>42</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>12</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>2.18</v>
       </c>
       <c r="CA20" t="n">
         <v>3.21</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CC20" t="n">
         <v>3.63</v>
@@ -8755,13 +8755,13 @@
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CG20" t="n">
         <v>2.5</v>
       </c>
       <c r="CH20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI20" t="n">
         <v>1.7</v>
@@ -8770,16 +8770,16 @@
         <v>2.06</v>
       </c>
       <c r="CK20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL20" t="n">
         <v>1.94</v>
       </c>
       <c r="CM20" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO20" t="n">
         <v>1.41</v>
@@ -8798,10 +8798,10 @@
         <v>1.79</v>
       </c>
       <c r="CW20" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CY20" t="n">
         <v>1.88</v>
@@ -8819,49 +8819,49 @@
         <v>2.26</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
       <c r="DE20" t="n">
         <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="DH20" t="n">
-        <v>77.95999999999999</v>
+        <v>78.78</v>
       </c>
       <c r="DI20" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.8</v>
+        <v>4.84</v>
       </c>
       <c r="DL20" t="n">
         <v>0.18</v>
       </c>
       <c r="DM20" t="n">
-        <v>34</v>
+        <v>34.86</v>
       </c>
       <c r="DN20" t="n">
         <v>1.14</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="DQ20" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="DR20" t="n">
-        <v>5.92</v>
+        <v>5.88</v>
       </c>
       <c r="DS20" t="n">
         <v>0.2</v>
@@ -8873,28 +8873,28 @@
         <v>0.02</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.64</v>
+        <v>47.88</v>
       </c>
       <c r="DW20" t="n">
         <v>0.22</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.34</v>
+        <v>12.41</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.380000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ20" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="EA20" t="n">
-        <v>10.28</v>
+        <v>10.53</v>
       </c>
       <c r="EB20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC20" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>24</v>
@@ -1786,49 +1786,49 @@
         <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>91.75</v>
+        <v>90.36</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>6.38</v>
+        <v>6.24</v>
       </c>
       <c r="L3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>42.67</v>
+        <v>41.72</v>
       </c>
       <c r="N3" t="n">
         <v>0.96</v>
       </c>
       <c r="O3" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
-        <v>11.54</v>
+        <v>11.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.33</v>
+        <v>6.6</v>
       </c>
       <c r="R3" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U3" t="n">
         <v>0.08</v>
@@ -1840,28 +1840,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.5</v>
+        <v>55.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.17</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.12</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AB3" t="n">
         <v>6.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.25</v>
+        <v>8.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1945,16 +1945,16 @@
         <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
         <v>0.31</v>
@@ -1963,46 +1963,46 @@
         <v>0.71</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
         <v>0.88</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.5</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>70.83</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>34.69</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.33</v>
+        <v>8.16</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>39.58</v>
+        <v>40.82</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="CA3" t="n">
         <v>3.31</v>
@@ -2023,13 +2023,13 @@
         <v>3.23</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH3" t="n">
         <v>1.31</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.13</v>
@@ -2053,7 +2053,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="CR3" t="n">
         <v>1.68</v>
@@ -2064,10 +2064,10 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX3" t="n">
         <v>1.78</v>
@@ -2082,55 +2082,55 @@
         <v>1.8</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="DE3" t="n">
         <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.02</v>
+        <v>90.33</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM3" t="n">
-        <v>39.23</v>
+        <v>38.82</v>
       </c>
       <c r="DN3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.73</v>
+        <v>11.76</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.71</v>
+        <v>6.84</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.18</v>
+        <v>5.34</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.25</v>
+        <v>52.92</v>
       </c>
       <c r="DW3" t="n">
         <v>0.23</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.88</v>
+        <v>13.84</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.73</v>
+        <v>4.76</v>
       </c>
       <c r="EA3" t="n">
-        <v>8.52</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="4">
@@ -2245,16 +2245,16 @@
         <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.27</v>
+        <v>14.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.77</v>
+        <v>8.82</v>
       </c>
       <c r="AB4" t="n">
         <v>5.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.27</v>
+        <v>9.32</v>
       </c>
       <c r="AD4" t="n">
         <v>1.6</v>
@@ -2407,7 +2407,7 @@
         <v>3.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC4" t="n">
         <v>3.5</v>
@@ -2483,7 +2483,7 @@
         <v>2.33</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
@@ -2543,16 +2543,16 @@
         <v>0.26</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.7</v>
+        <v>12.72</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.61</v>
       </c>
       <c r="EA4" t="n">
-        <v>9.93</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="EB4" t="n">
         <v>1.41</v>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>24</v>
@@ -2580,82 +2580,82 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="H5" t="n">
-        <v>97.79000000000001</v>
+        <v>97.84</v>
       </c>
       <c r="I5" t="n">
         <v>-0.04</v>
       </c>
       <c r="J5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="K5" t="n">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="M5" t="n">
-        <v>42.96</v>
+        <v>43.8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="P5" t="n">
-        <v>12.33</v>
+        <v>12.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="R5" t="n">
-        <v>4.12</v>
+        <v>4.32</v>
       </c>
       <c r="S5" t="n">
         <v>0.88</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.71</v>
+        <v>59.72</v>
       </c>
       <c r="Y5" t="n">
         <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.25</v>
+        <v>18.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.75</v>
+        <v>12.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.17</v>
+        <v>12.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AF5" t="n">
         <v>0.12</v>
@@ -2739,58 +2739,58 @@
         <v>2.75</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="BK5" t="n">
         <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BP5" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>4.67</v>
       </c>
-      <c r="BQ5" t="n">
-        <v>4.62</v>
-      </c>
       <c r="BR5" t="n">
-        <v>87.5</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>70.83</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.25</v>
+        <v>55.1</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.08</v>
+        <v>26.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.58</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>8.16</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.25</v>
+        <v>57.14</v>
       </c>
       <c r="BY5" t="n">
         <v>1.51</v>
@@ -2799,7 +2799,7 @@
         <v>1.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB5" t="n">
         <v>3.83</v>
@@ -2814,7 +2814,7 @@
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CG5" t="n">
         <v>2.78</v>
@@ -2835,7 +2835,7 @@
         <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN5" t="n">
         <v>1.72</v>
@@ -2844,20 +2844,20 @@
         <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
@@ -2874,19 +2874,19 @@
         <v>1.98</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.25</v>
+        <v>92.39</v>
       </c>
       <c r="DI5" t="n">
         <v>0.04</v>
@@ -2898,58 +2898,58 @@
         <v>5.9</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.08</v>
+        <v>40.57</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.54</v>
+        <v>11.59</v>
       </c>
       <c r="DQ5" t="n">
-        <v>7.32</v>
+        <v>7.37</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.29</v>
+        <v>57.35</v>
       </c>
       <c r="DW5" t="n">
         <v>0.29</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.88</v>
+        <v>16.14</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.38</v>
+        <v>10.57</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>10.12</v>
+        <v>10.37</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="6">
@@ -5585,7 +5585,7 @@
         <v>4.06</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
@@ -5655,7 +5655,7 @@
         <v>2.45</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="DE12" t="n">
         <v>0.03</v>
@@ -5740,13 +5740,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
         <v>0.16</v>
@@ -5833,49 +5833,49 @@
         <v>0.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AI13" t="n">
-        <v>90.88</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="AJ13" t="n">
         <v>-0.04</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.52</v>
+        <v>5.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.52</v>
+        <v>42.27</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.52</v>
+        <v>9.65</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.24</v>
+        <v>7.46</v>
       </c>
       <c r="AS13" t="n">
         <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AV13" t="n">
         <v>0.12</v>
@@ -5887,82 +5887,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.64</v>
+        <v>54</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.32</v>
+        <v>14.46</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BC13" t="n">
         <v>4.96</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.32</v>
+        <v>9.65</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
         <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="BR13" t="n">
-        <v>88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>68</v>
+        <v>68.63</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>41.18</v>
       </c>
       <c r="BU13" t="n">
-        <v>22</v>
+        <v>21.57</v>
       </c>
       <c r="BV13" t="n">
-        <v>12</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="BX13" t="n">
-        <v>48</v>
+        <v>49.02</v>
       </c>
       <c r="BY13" t="n">
         <v>1.73</v>
@@ -5974,13 +5974,13 @@
         <v>3.32</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CC13" t="n">
         <v>2.49</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CE13" t="n">
         <v>1.42</v>
@@ -5995,7 +5995,7 @@
         <v>1.3</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.02</v>
@@ -6004,13 +6004,13 @@
         <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM13" t="n">
         <v>2</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO13" t="n">
         <v>1.33</v>
@@ -6030,10 +6030,10 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX13" t="n">
         <v>1.77</v>
@@ -6054,46 +6054,46 @@
         <v>2.18</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="DE13" t="n">
         <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DH13" t="n">
-        <v>92.34</v>
+        <v>92.45</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.02</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.74</v>
+        <v>43.1</v>
       </c>
       <c r="DN13" t="n">
         <v>1.22</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>7.1</v>
+        <v>7.21</v>
       </c>
       <c r="DR13" t="n">
         <v>4.76</v>
@@ -6108,28 +6108,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.54</v>
+        <v>56.67</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.84</v>
+        <v>15.88</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.52</v>
+        <v>10.57</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.32</v>
+        <v>5.31</v>
       </c>
       <c r="EA13" t="n">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
         <v>0.25</v>
@@ -6232,103 +6232,103 @@
         <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
         <v>1.88</v>
       </c>
       <c r="AI14" t="n">
-        <v>82.54000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="AJ14" t="n">
         <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AN14" t="n">
-        <v>34.38</v>
+        <v>34.04</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.75</v>
+        <v>9.76</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.75</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.71</v>
+        <v>6.08</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.92</v>
+        <v>50.48</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.75</v>
+        <v>9.76</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.08</v>
+        <v>9.06</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
         <v>0.73</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
         <v>1.31</v>
@@ -6337,31 +6337,31 @@
         <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.71</v>
+        <v>4.76</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.67</v>
+        <v>91.84</v>
       </c>
       <c r="BS14" t="n">
-        <v>70.83</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>43.75</v>
+        <v>42.86</v>
       </c>
       <c r="BU14" t="n">
-        <v>20.83</v>
+        <v>20.41</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.42</v>
+        <v>10.2</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.08</v>
+        <v>53.06</v>
       </c>
       <c r="BY14" t="n">
         <v>1.82</v>
@@ -6370,34 +6370,34 @@
         <v>1.85</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CK14" t="n">
         <v>1.63</v>
@@ -6412,20 +6412,20 @@
         <v>1.64</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP14" t="n">
         <v>2.15</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW14" t="n">
         <v>2</v>
@@ -6440,91 +6440,91 @@
         <v>1.87</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB14" t="n">
         <v>1.36</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="DE14" t="n">
         <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.42</v>
+        <v>84.16</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.57</v>
+        <v>38.31</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="DP14" t="n">
         <v>10.1</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.25</v>
+        <v>7.39</v>
       </c>
       <c r="DR14" t="n">
-        <v>4.92</v>
+        <v>5.12</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU14" t="n">
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.32</v>
+        <v>53.04</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.73</v>
+        <v>11.61</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.78</v>
+        <v>7.72</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="EA14" t="n">
-        <v>8.92</v>
+        <v>8.94</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>0.14</v>
@@ -2263,52 +2263,52 @@
         <v>3.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AI4" t="n">
-        <v>83.38</v>
+        <v>83.86</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.43</v>
+        <v>4.59</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.81</v>
+        <v>37.36</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.33</v>
+        <v>10.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.86</v>
+        <v>7.91</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AV4" t="n">
         <v>0.14</v>
@@ -2320,82 +2320,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.52</v>
+        <v>49.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.38</v>
+        <v>7.45</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="BD4" t="n">
-        <v>10.62</v>
+        <v>11</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.84</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO4" t="n">
         <v>1.14</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.23</v>
+        <v>4.27</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.37</v>
+        <v>88.64</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.77</v>
+        <v>70.45</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.51</v>
+        <v>45.45</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.28</v>
+        <v>15.91</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.51</v>
+        <v>45.45</v>
       </c>
       <c r="BY4" t="n">
         <v>1.97</v>
@@ -2407,16 +2407,16 @@
         <v>3.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF4" t="n">
         <v>3.35</v>
@@ -2437,7 +2437,7 @@
         <v>1.56</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM4" t="n">
         <v>2.03</v>
@@ -2459,10 +2459,10 @@
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CX4" t="n">
         <v>1.82</v>
@@ -2477,52 +2477,52 @@
         <v>1.78</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.3</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.91</v>
+        <v>40.11</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.26</v>
+        <v>11.12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.68</v>
+        <v>6.73</v>
       </c>
       <c r="DR4" t="n">
         <v>4.05</v>
@@ -2534,28 +2534,28 @@
         <v>0.19</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.28</v>
+        <v>53.59</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.72</v>
+        <v>12.78</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.119999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="EA4" t="n">
-        <v>9.949999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
         <v>2.88</v>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2661,136 +2661,136 @@
         <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.70999999999999</v>
+        <v>86.48</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>37.21</v>
+        <v>37.32</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.75</v>
+        <v>10.84</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.88</v>
+        <v>7.96</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.62</v>
+        <v>5.88</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.88</v>
+        <v>54.44</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.5</v>
+        <v>13.72</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH5" t="n">
         <v>9.76</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.59</v>
+        <v>4.48</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="BR5" t="n">
-        <v>87.76000000000001</v>
+        <v>88</v>
       </c>
       <c r="BS5" t="n">
-        <v>71.43000000000001</v>
+        <v>72</v>
       </c>
       <c r="BT5" t="n">
-        <v>55.1</v>
+        <v>56</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.53</v>
+        <v>26</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>14</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.16</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.14</v>
+        <v>58</v>
       </c>
       <c r="BY5" t="n">
         <v>1.51</v>
@@ -2799,16 +2799,16 @@
         <v>1.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CE5" t="n">
         <v>1.4</v>
@@ -2823,10 +2823,10 @@
         <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK5" t="n">
         <v>1.51</v>
@@ -2874,19 +2874,19 @@
         <v>1.98</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.39</v>
+        <v>92.16</v>
       </c>
       <c r="DI5" t="n">
         <v>0.04</v>
@@ -2898,58 +2898,58 @@
         <v>5.9</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.57</v>
+        <v>40.56</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.59</v>
+        <v>11.62</v>
       </c>
       <c r="DQ5" t="n">
-        <v>7.37</v>
+        <v>7.42</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.96</v>
+        <v>5.1</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.35</v>
+        <v>57.08</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.14</v>
+        <v>16.2</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.57</v>
+        <v>10.58</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.57</v>
+        <v>5.62</v>
       </c>
       <c r="EA5" t="n">
-        <v>10.37</v>
+        <v>10.42</v>
       </c>
       <c r="EB5" t="n">
         <v>1.71</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="6">
@@ -3354,61 +3354,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
         <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H7" t="n">
-        <v>85.04000000000001</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>34.58</v>
+        <v>35.04</v>
       </c>
       <c r="N7" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>11.12</v>
+        <v>11.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.38</v>
+        <v>6.68</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U7" t="n">
         <v>0.08</v>
@@ -3420,28 +3420,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.42</v>
+        <v>54.4</v>
       </c>
       <c r="Y7" t="n">
         <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>14.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.58</v>
+        <v>9.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.42</v>
+        <v>4.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3525,67 +3525,67 @@
         <v>2.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
         <v>1.04</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="BR7" t="n">
-        <v>87.76000000000001</v>
+        <v>88</v>
       </c>
       <c r="BS7" t="n">
-        <v>67.34999999999999</v>
+        <v>66</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>42</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.53</v>
+        <v>26</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.16</v>
+        <v>8</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BX7" t="n">
-        <v>51.02</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>1.94</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CB7" t="n">
         <v>3.28</v>
@@ -3600,19 +3600,19 @@
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK7" t="n">
         <v>1.59</v>
@@ -3621,19 +3621,19 @@
         <v>2.04</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO7" t="n">
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="CR7" t="n">
         <v>1.68</v>
@@ -3668,49 +3668,49 @@
         <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="DE7" t="n">
         <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.94</v>
+        <v>80.88</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="DK7" t="n">
         <v>4.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.81</v>
+        <v>34.06</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.06</v>
+        <v>10.1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6.06</v>
+        <v>6.22</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3722,28 +3722,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.31</v>
+        <v>53.32</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.16</v>
+        <v>12.28</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.96</v>
+        <v>8</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="EA7" t="n">
-        <v>9.41</v>
+        <v>9.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="8">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
         <v>22</v>
@@ -5357,82 +5357,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G12" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>86.14</v>
+        <v>85.36</v>
       </c>
       <c r="I12" t="n">
         <v>0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="K12" t="n">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="L12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="M12" t="n">
-        <v>34.24</v>
+        <v>33.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="O12" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="P12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
       <c r="R12" t="n">
-        <v>4.81</v>
+        <v>5.27</v>
       </c>
       <c r="S12" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="U12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.81</v>
+        <v>51.91</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>12.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.1</v>
+        <v>11.41</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="AF12" t="n">
         <v>0.05</v>
@@ -5516,25 +5516,25 @@
         <v>2.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="BN12" t="n">
         <v>1.14</v>
@@ -5543,43 +5543,43 @@
         <v>0.98</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.37</v>
+        <v>88.64</v>
       </c>
       <c r="BS12" t="n">
-        <v>62.79</v>
+        <v>63.64</v>
       </c>
       <c r="BT12" t="n">
-        <v>34.88</v>
+        <v>34.09</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.6</v>
+        <v>18.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="BX12" t="n">
-        <v>39.53</v>
+        <v>38.64</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CA12" t="n">
         <v>3.1</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CC12" t="n">
         <v>4.06</v>
@@ -5591,7 +5591,7 @@
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CG12" t="n">
         <v>2.4</v>
@@ -5634,7 +5634,7 @@
         <v>1.71</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX12" t="n">
         <v>1.8</v>
@@ -5655,82 +5655,82 @@
         <v>2.45</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.77</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.58</v>
+        <v>4.52</v>
       </c>
       <c r="DL12" t="n">
         <v>0.48</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.93</v>
+        <v>32.59</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="DP12" t="n">
         <v>10.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.58</v>
+        <v>6.55</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.56</v>
+        <v>4.8</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.84</v>
+        <v>52.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.65</v>
+        <v>12.52</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.81</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="EA12" t="n">
-        <v>10.45</v>
+        <v>10.62</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="13">
@@ -6139,94 +6139,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
         <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="H14" t="n">
-        <v>86.29000000000001</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0.04</v>
       </c>
       <c r="J14" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K14" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>42.75</v>
+        <v>43.24</v>
       </c>
       <c r="N14" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="O14" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>10.46</v>
+        <v>10.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.75</v>
+        <v>6.04</v>
       </c>
       <c r="R14" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="S14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U14" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="W14" t="n">
         <v>0.04</v>
       </c>
       <c r="X14" t="n">
-        <v>55.71</v>
+        <v>55.72</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.29</v>
+        <v>13.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.08</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6310,70 +6310,70 @@
         <v>2.68</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.06</v>
+        <v>9.08</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BO14" t="n">
         <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.76</v>
+        <v>4.64</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.84</v>
+        <v>92</v>
       </c>
       <c r="BS14" t="n">
-        <v>71.43000000000001</v>
+        <v>72</v>
       </c>
       <c r="BT14" t="n">
-        <v>42.86</v>
+        <v>44</v>
       </c>
       <c r="BU14" t="n">
-        <v>20.41</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="BW14" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BX14" t="n">
-        <v>53.06</v>
+        <v>54</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC14" t="n">
         <v>3.76</v>
@@ -6385,7 +6385,7 @@
         <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG14" t="n">
         <v>2.61</v>
@@ -6406,7 +6406,7 @@
         <v>2.1</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CN14" t="n">
         <v>1.64</v>
@@ -6415,10 +6415,10 @@
         <v>1.37</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
@@ -6428,7 +6428,7 @@
         <v>1.85</v>
       </c>
       <c r="CW14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX14" t="n">
         <v>1.81</v>
@@ -6440,7 +6440,7 @@
         <v>1.87</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.36</v>
@@ -6449,49 +6449,49 @@
         <v>2.14</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="DE14" t="n">
         <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.16</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.31</v>
+        <v>38.64</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="DP14" t="n">
         <v>10.1</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.39</v>
+        <v>7.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.12</v>
+        <v>5.18</v>
       </c>
       <c r="DS14" t="n">
         <v>0.22</v>
@@ -6503,28 +6503,28 @@
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.04</v>
+        <v>53.1</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.61</v>
+        <v>11.7</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.72</v>
+        <v>7.8</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.9</v>
       </c>
       <c r="EA14" t="n">
-        <v>8.94</v>
+        <v>9.06</v>
       </c>
       <c r="EB14" t="n">
         <v>1.3</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="15">
@@ -8509,13 +8509,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
         <v>0.08</v>
@@ -8602,52 +8602,52 @@
         <v>0.12</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>70.52</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="AK20" t="n">
         <v>3.88</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="AM20" t="n">
         <v>0.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>28.8</v>
+        <v>29.23</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.92</v>
+        <v>11.04</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.44</v>
+        <v>7.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.56</v>
+        <v>7.73</v>
       </c>
       <c r="AT20" t="n">
         <v>1.12</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AW20" t="n">
         <v>0.12</v>
@@ -8656,82 +8656,82 @@
         <v>0.04</v>
       </c>
       <c r="AY20" t="n">
-        <v>42.64</v>
+        <v>42.77</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.16</v>
+        <v>10.19</v>
       </c>
       <c r="BB20" t="n">
         <v>6.88</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="BD20" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.24</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BL20" t="n">
         <v>0.63</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.76</v>
+        <v>4.79</v>
       </c>
       <c r="BR20" t="n">
-        <v>86.27</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="BS20" t="n">
-        <v>64.70999999999999</v>
+        <v>63.46</v>
       </c>
       <c r="BT20" t="n">
-        <v>43.14</v>
+        <v>42.31</v>
       </c>
       <c r="BU20" t="n">
-        <v>11.76</v>
+        <v>11.54</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.88</v>
+        <v>5.77</v>
       </c>
       <c r="BW20" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="BX20" t="n">
-        <v>49.02</v>
+        <v>48.08</v>
       </c>
       <c r="BY20" t="n">
         <v>2.07</v>
@@ -8740,13 +8740,13 @@
         <v>2.2</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CB20" t="n">
         <v>3.4</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CD20" t="n">
         <v>4.62</v>
@@ -8779,16 +8779,16 @@
         <v>2.23</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO20" t="n">
         <v>1.41</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CR20" t="inlineStr"/>
       <c r="CS20" t="inlineStr"/>
@@ -8810,7 +8810,7 @@
         <v>1.87</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB20" t="n">
         <v>1.39</v>
@@ -8819,52 +8819,52 @@
         <v>2.26</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="DE20" t="n">
         <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="DH20" t="n">
-        <v>78.78</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="DJ20" t="n">
         <v>3.51</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.84</v>
+        <v>4.82</v>
       </c>
       <c r="DL20" t="n">
         <v>0.18</v>
       </c>
       <c r="DM20" t="n">
-        <v>34.86</v>
+        <v>34.96</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.08</v>
+        <v>11.14</v>
       </c>
       <c r="DQ20" t="n">
-        <v>7.02</v>
+        <v>7.12</v>
       </c>
       <c r="DR20" t="n">
-        <v>5.88</v>
+        <v>6</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT20" t="n">
         <v>0.18</v>
@@ -8873,22 +8873,22 @@
         <v>0.02</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.88</v>
+        <v>47.84</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.41</v>
+        <v>12.38</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.369999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="DZ20" t="n">
         <v>4.04</v>
       </c>
       <c r="EA20" t="n">
-        <v>10.53</v>
+        <v>10.69</v>
       </c>
       <c r="EB20" t="n">
         <v>1.31</v>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
@@ -1867,43 +1867,43 @@
         <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AI3" t="n">
-        <v>90.29000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.17</v>
+        <v>4.04</v>
       </c>
       <c r="AM3" t="n">
         <v>-0.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>35.79</v>
+        <v>35.16</v>
       </c>
       <c r="AO3" t="n">
         <v>0.92</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.92</v>
+        <v>11.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.08</v>
+        <v>7.28</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.12</v>
+        <v>6.32</v>
       </c>
       <c r="AT3" t="n">
         <v>0.92</v>
@@ -1921,82 +1921,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50</v>
+        <v>49.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.58</v>
+        <v>11.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.17</v>
+        <v>7.96</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BG3" t="n">
         <v>2.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.51</v>
+        <v>9.4</v>
       </c>
       <c r="BI3" t="n">
         <v>2.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.76000000000001</v>
+        <v>88</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>72</v>
       </c>
       <c r="BT3" t="n">
-        <v>34.69</v>
+        <v>34</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.16</v>
+        <v>8</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BX3" t="n">
-        <v>40.82</v>
+        <v>42</v>
       </c>
       <c r="BY3" t="n">
         <v>1.9</v>
@@ -2005,25 +2005,25 @@
         <v>2.04</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.32</v>
+        <v>3.49</v>
       </c>
       <c r="CE3" t="n">
         <v>1.48</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CH3" t="n">
         <v>1.31</v>
@@ -2032,7 +2032,7 @@
         <v>1.66</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CK3" t="n">
         <v>1.57</v>
@@ -2047,13 +2047,13 @@
         <v>1.62</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CR3" t="n">
         <v>1.68</v>
@@ -2064,10 +2064,10 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX3" t="n">
         <v>1.78</v>
@@ -2085,22 +2085,22 @@
         <v>1.44</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="DE3" t="n">
         <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.33</v>
+        <v>89.5</v>
       </c>
       <c r="DI3" t="n">
         <v>0.1</v>
@@ -2109,28 +2109,28 @@
         <v>2.78</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="DL3" t="n">
         <v>0.18</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.82</v>
+        <v>38.44</v>
       </c>
       <c r="DN3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.76</v>
+        <v>11.7</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.34</v>
+        <v>5.46</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.92</v>
+        <v>52.56</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.84</v>
+        <v>13.7</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.08</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.76</v>
+        <v>4.74</v>
       </c>
       <c r="EA3" t="n">
-        <v>8.550000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="4">
@@ -2664,7 +2664,7 @@
         <v>1.68</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AI5" t="n">
         <v>86.48</v>
@@ -2679,7 +2679,7 @@
         <v>5.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="AN5" t="n">
         <v>37.32</v>
@@ -2688,7 +2688,7 @@
         <v>1.56</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AQ5" t="n">
         <v>10.84</v>
@@ -2766,10 +2766,10 @@
         <v>1.46</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.48</v>
+        <v>4.58</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="BR5" t="n">
         <v>88</v>
@@ -2883,7 +2883,7 @@
         <v>1.44</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="DH5" t="n">
         <v>92.16</v>
@@ -2898,7 +2898,7 @@
         <v>5.9</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
         <v>40.56</v>
@@ -2907,7 +2907,7 @@
         <v>1.4</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
         <v>11.62</v>
@@ -5740,94 +5740,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
         <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F13" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="G13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H13" t="n">
-        <v>93.8</v>
+        <v>95.31</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="K13" t="n">
-        <v>5.68</v>
+        <v>5.58</v>
       </c>
       <c r="L13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="M13" t="n">
-        <v>43.96</v>
+        <v>44.27</v>
       </c>
       <c r="N13" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="O13" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="P13" t="n">
-        <v>12.4</v>
+        <v>12.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.96</v>
+        <v>7.04</v>
       </c>
       <c r="R13" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="V13" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>59.44</v>
+        <v>59.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.36</v>
+        <v>17.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.68</v>
+        <v>11.69</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.68</v>
+        <v>8.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AF13" t="n">
         <v>0.12</v>
@@ -5911,70 +5911,70 @@
         <v>2.69</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.08</v>
+        <v>8.98</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.23999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.63</v>
+        <v>69.23</v>
       </c>
       <c r="BT13" t="n">
-        <v>41.18</v>
+        <v>40.38</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.57</v>
+        <v>21.15</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.54</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.84</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>49.02</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CC13" t="n">
         <v>2.49</v>
@@ -5986,10 +5986,10 @@
         <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH13" t="n">
         <v>1.3</v>
@@ -5998,28 +5998,28 @@
         <v>1.69</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
         <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN13" t="n">
         <v>1.59</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CR13" t="n">
         <v>1.68</v>
@@ -6051,52 +6051,52 @@
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DG13" t="n">
         <v>2.37</v>
       </c>
       <c r="DH13" t="n">
-        <v>92.45</v>
+        <v>93.23</v>
       </c>
       <c r="DI13" t="n">
         <v>-0.02</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.59</v>
+        <v>5.54</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.1</v>
+        <v>43.27</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="DQ13" t="n">
-        <v>7.21</v>
+        <v>7.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.76</v>
+        <v>4.71</v>
       </c>
       <c r="DS13" t="n">
         <v>0.18</v>
@@ -6108,28 +6108,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.67</v>
+        <v>56.82</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.88</v>
+        <v>15.92</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.57</v>
+        <v>10.6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.31</v>
+        <v>5.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>8.68</v>
+        <v>8.9</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="14">
@@ -6154,7 +6154,7 @@
         <v>1.48</v>
       </c>
       <c r="G14" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="H14" t="n">
         <v>86.68000000000001</v>
@@ -6169,7 +6169,7 @@
         <v>5.32</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="M14" t="n">
         <v>43.24</v>
@@ -6178,7 +6178,7 @@
         <v>1.16</v>
       </c>
       <c r="O14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>10.44</v>
@@ -6337,10 +6337,10 @@
         <v>1.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.02</v>
+        <v>4.12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.64</v>
+        <v>4.78</v>
       </c>
       <c r="BR14" t="n">
         <v>92</v>
@@ -6458,7 +6458,7 @@
         <v>1.54</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="DH14" t="n">
         <v>84.40000000000001</v>
@@ -6473,7 +6473,7 @@
         <v>4.64</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DM14" t="n">
         <v>38.64</v>
@@ -6482,7 +6482,7 @@
         <v>1.28</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP14" t="n">
         <v>10.1</v>

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
@@ -1867,46 +1867,46 @@
         <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AI3" t="n">
-        <v>88.64</v>
+        <v>88.92</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="AM3" t="n">
         <v>-0.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>35.16</v>
+        <v>35.19</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.8</v>
+        <v>11.96</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.28</v>
+        <v>7.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AU3" t="n">
         <v>0.88</v>
@@ -1921,82 +1921,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>49.4</v>
+        <v>49.42</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.4</v>
+        <v>11.38</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.96</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.960000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="BR3" t="n">
-        <v>88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>72</v>
+        <v>72.55</v>
       </c>
       <c r="BT3" t="n">
-        <v>34</v>
+        <v>35.29</v>
       </c>
       <c r="BU3" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="BV3" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="BW3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BX3" t="n">
-        <v>42</v>
+        <v>43.14</v>
       </c>
       <c r="BY3" t="n">
         <v>1.9</v>
@@ -2005,34 +2005,34 @@
         <v>2.04</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CB3" t="n">
         <v>3.43</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.49</v>
+        <v>3.54</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CH3" t="n">
         <v>1.31</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK3" t="n">
         <v>1.57</v>
@@ -2041,7 +2041,7 @@
         <v>2.03</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN3" t="n">
         <v>1.62</v>
@@ -2050,10 +2050,10 @@
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CR3" t="n">
         <v>1.68</v>
@@ -2064,10 +2064,10 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX3" t="n">
         <v>1.78</v>
@@ -2079,58 +2079,58 @@
         <v>1.9</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="DE3" t="n">
         <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.5</v>
+        <v>89.63</v>
       </c>
       <c r="DI3" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="DL3" t="n">
         <v>0.18</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.44</v>
+        <v>38.39</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.7</v>
+        <v>11.78</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.56</v>
+        <v>52.51</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.7</v>
+        <v>13.64</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.960000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="EA3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="4">
@@ -2173,94 +2173,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="H4" t="n">
-        <v>93</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J4" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="K4" t="n">
-        <v>5.41</v>
+        <v>5.35</v>
       </c>
       <c r="L4" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>42.86</v>
+        <v>42.96</v>
       </c>
       <c r="N4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O4" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>12.14</v>
+        <v>12.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.55</v>
+        <v>5.96</v>
       </c>
       <c r="R4" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="S4" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0.09</v>
       </c>
       <c r="X4" t="n">
-        <v>57.82</v>
+        <v>57.61</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.32</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.82</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.32</v>
+        <v>10.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.09</v>
+        <v>3.26</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2344,70 +2344,70 @@
         <v>2.68</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BN4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.11</v>
       </c>
-      <c r="BO4" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BP4" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.64</v>
+        <v>86.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.45</v>
+        <v>68.89</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.45</v>
+        <v>44.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.91</v>
+        <v>15.56</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.45</v>
+        <v>44.44</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CC4" t="n">
         <v>3.47</v>
@@ -2428,13 +2428,13 @@
         <v>1.29</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL4" t="n">
         <v>2.05</v>
@@ -2459,19 +2459,19 @@
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY4" t="n">
         <v>1.9</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DA4" t="n">
         <v>1.78</v>
@@ -2480,85 +2480,85 @@
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="DG4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DO4" t="n">
         <v>2.38</v>
       </c>
-      <c r="DH4" t="n">
-        <v>88.43000000000001</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>5</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>40.11</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>2.35</v>
-      </c>
       <c r="DP4" t="n">
-        <v>11.12</v>
+        <v>11.29</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.73</v>
+        <v>6.91</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.59</v>
+        <v>53.58</v>
       </c>
       <c r="DW4" t="n">
         <v>0.27</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.78</v>
+        <v>12.65</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.64</v>
+        <v>4.55</v>
       </c>
       <c r="EA4" t="n">
-        <v>10.16</v>
+        <v>10.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="5">
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>25</v>
@@ -2580,43 +2580,43 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="G5" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>97.84</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="L5" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>43.8</v>
+        <v>42.96</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="P5" t="n">
-        <v>12.4</v>
+        <v>12.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.88</v>
+        <v>7.23</v>
       </c>
       <c r="R5" t="n">
-        <v>4.32</v>
+        <v>4.54</v>
       </c>
       <c r="S5" t="n">
         <v>0.88</v>
@@ -2625,37 +2625,37 @@
         <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.72</v>
+        <v>59.04</v>
       </c>
       <c r="Y5" t="n">
         <v>0.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.68</v>
+        <v>18.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.08</v>
+        <v>11.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.6</v>
+        <v>6.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.56</v>
+        <v>12.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.12</v>
@@ -2739,70 +2739,70 @@
         <v>2.76</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.76</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.78</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
         <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="BR5" t="n">
-        <v>88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>72</v>
+        <v>72.55</v>
       </c>
       <c r="BT5" t="n">
-        <v>56</v>
+        <v>56.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>26</v>
+        <v>25.49</v>
       </c>
       <c r="BV5" t="n">
-        <v>14</v>
+        <v>13.73</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="BX5" t="n">
-        <v>58</v>
+        <v>58.82</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC5" t="n">
         <v>2.26</v>
@@ -2814,7 +2814,7 @@
         <v>1.4</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CG5" t="n">
         <v>2.78</v>
@@ -2847,17 +2847,17 @@
         <v>2.02</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CR5" t="inlineStr"/>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="inlineStr"/>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="CZ5" t="inlineStr"/>
       <c r="DA5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
@@ -2880,76 +2880,76 @@
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.16</v>
+        <v>92.02</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.56</v>
+        <v>40.2</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.62</v>
+        <v>11.75</v>
       </c>
       <c r="DQ5" t="n">
-        <v>7.42</v>
+        <v>7.59</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.08</v>
+        <v>56.79</v>
       </c>
       <c r="DW5" t="n">
         <v>0.28</v>
       </c>
       <c r="DX5" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.58</v>
+        <v>10.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.62</v>
+        <v>5.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>10.42</v>
+        <v>10.53</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="6">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -3444,52 +3444,52 @@
         <v>2.92</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" t="n">
-        <v>77</v>
+        <v>77.42</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.08</v>
+        <v>33</v>
       </c>
       <c r="AO7" t="n">
         <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.039999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.76</v>
+        <v>6.35</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.52</v>
+        <v>5.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3501,82 +3501,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.24</v>
+        <v>52.04</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="BD7" t="n">
-        <v>10.12</v>
+        <v>10.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BF7" t="n">
         <v>2.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="BR7" t="n">
-        <v>88</v>
+        <v>86.27</v>
       </c>
       <c r="BS7" t="n">
-        <v>66</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>42</v>
+        <v>41.18</v>
       </c>
       <c r="BU7" t="n">
-        <v>26</v>
+        <v>25.49</v>
       </c>
       <c r="BV7" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="BW7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>49.02</v>
       </c>
       <c r="BY7" t="n">
         <v>1.94</v>
@@ -3588,13 +3588,13 @@
         <v>3.27</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CE7" t="n">
         <v>1.48</v>
@@ -3603,10 +3603,10 @@
         <v>3.3</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI7" t="n">
         <v>1.67</v>
@@ -3630,10 +3630,10 @@
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="CR7" t="n">
         <v>1.68</v>
@@ -3650,13 +3650,13 @@
         <v>2.07</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CY7" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DA7" t="n">
         <v>1.77</v>
@@ -3665,52 +3665,52 @@
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DG7" t="n">
         <v>1.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.88</v>
+        <v>81.02</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DK7" t="n">
         <v>4.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.06</v>
+        <v>34</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.1</v>
+        <v>10.22</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6.22</v>
+        <v>6.51</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3722,28 +3722,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.32</v>
+        <v>53.2</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.28</v>
+        <v>12.18</v>
       </c>
       <c r="DY7" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
       <c r="EA7" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="8">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
         <v>22</v>
@@ -5357,82 +5357,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H12" t="n">
-        <v>85.36</v>
+        <v>85.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="J12" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="K12" t="n">
-        <v>5.27</v>
+        <v>5.39</v>
       </c>
       <c r="L12" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="M12" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O12" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="P12" t="n">
-        <v>9.640000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.27</v>
+        <v>5.52</v>
       </c>
       <c r="R12" t="n">
-        <v>5.27</v>
+        <v>5.52</v>
       </c>
       <c r="S12" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="T12" t="n">
         <v>1.09</v>
       </c>
       <c r="U12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.91</v>
+        <v>51.57</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.73</v>
+        <v>12.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="AD12" t="n">
         <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="AF12" t="n">
         <v>0.05</v>
@@ -5516,64 +5516,64 @@
         <v>2.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.32</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.68</v>
+        <v>4.76</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.64</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>63.64</v>
+        <v>64.44</v>
       </c>
       <c r="BT12" t="n">
-        <v>34.09</v>
+        <v>35.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>17.78</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BX12" t="n">
-        <v>38.64</v>
+        <v>40</v>
       </c>
       <c r="BY12" t="n">
         <v>2.39</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="CA12" t="n">
         <v>3.1</v>
@@ -5591,19 +5591,19 @@
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK12" t="n">
         <v>1.55</v>
@@ -5612,38 +5612,38 @@
         <v>2.02</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN12" t="n">
         <v>1.68</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
       <c r="CT12" t="inlineStr"/>
       <c r="CU12" t="inlineStr"/>
       <c r="CV12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CY12" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DA12" t="n">
         <v>1.8</v>
@@ -5652,52 +5652,52 @@
         <v>1.46</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="DE12" t="n">
         <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.45999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.59</v>
+        <v>32.51</v>
       </c>
       <c r="DN12" t="n">
         <v>0.93</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.55</v>
+        <v>6.64</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5709,16 +5709,16 @@
         <v>0.02</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.38</v>
+        <v>52.2</v>
       </c>
       <c r="DW12" t="n">
         <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.52</v>
+        <v>12.51</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.8</v>
@@ -5730,7 +5730,7 @@
         <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5740,13 +5740,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n">
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
         <v>0.15</v>
@@ -5830,139 +5830,139 @@
         <v>2.96</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AI13" t="n">
-        <v>91.15000000000001</v>
+        <v>91.11</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.5</v>
+        <v>5.37</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.27</v>
+        <v>42.37</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.46</v>
+        <v>7.81</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>54</v>
+        <v>54.15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.46</v>
+        <v>14.44</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.5</v>
+        <v>9.56</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.96</v>
+        <v>4.89</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.65</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.98</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="BM13" t="n">
         <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BO13" t="n">
         <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.45999999999999</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.23</v>
+        <v>69.81</v>
       </c>
       <c r="BT13" t="n">
-        <v>40.38</v>
+        <v>41.51</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.15</v>
+        <v>20.75</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.54</v>
+        <v>11.32</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.55</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>50.94</v>
       </c>
       <c r="BY13" t="n">
         <v>1.72</v>
@@ -5977,31 +5977,31 @@
         <v>3.4</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CE13" t="n">
         <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG13" t="n">
         <v>2.54</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL13" t="n">
         <v>1.96</v>
@@ -6030,10 +6030,10 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX13" t="n">
         <v>1.77</v>
@@ -6048,88 +6048,88 @@
         <v>1.8</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC13" t="n">
         <v>2.16</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="DE13" t="n">
         <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DH13" t="n">
-        <v>93.23</v>
+        <v>93.17</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.54</v>
+        <v>5.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.27</v>
+        <v>43.3</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.04</v>
+        <v>11.13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>7.25</v>
+        <v>7.43</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.71</v>
+        <v>4.74</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.82</v>
+        <v>56.85</v>
       </c>
       <c r="DW13" t="n">
         <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.92</v>
+        <v>15.88</v>
       </c>
       <c r="DY13" t="n">
         <v>10.6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="EA13" t="n">
-        <v>8.9</v>
+        <v>9.09</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -6139,94 +6139,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
         <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F14" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="G14" t="n">
         <v>3.04</v>
       </c>
       <c r="H14" t="n">
-        <v>86.68000000000001</v>
+        <v>87.12</v>
       </c>
       <c r="I14" t="n">
         <v>0.04</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="L14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="M14" t="n">
-        <v>43.24</v>
+        <v>42.65</v>
       </c>
       <c r="N14" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>10.44</v>
+        <v>10.54</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.04</v>
+        <v>6.42</v>
       </c>
       <c r="R14" t="n">
-        <v>4.28</v>
+        <v>4.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="W14" t="n">
         <v>0.04</v>
       </c>
       <c r="X14" t="n">
-        <v>55.72</v>
+        <v>55.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.4</v>
+        <v>13.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.359999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6310,58 +6310,58 @@
         <v>2.68</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.08</v>
+        <v>9.02</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="BR14" t="n">
-        <v>92</v>
+        <v>92.16</v>
       </c>
       <c r="BS14" t="n">
-        <v>72</v>
+        <v>72.55</v>
       </c>
       <c r="BT14" t="n">
-        <v>44</v>
+        <v>45.1</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>19.61</v>
       </c>
       <c r="BV14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BX14" t="n">
-        <v>54</v>
+        <v>54.9</v>
       </c>
       <c r="BY14" t="n">
         <v>1.84</v>
@@ -6385,25 +6385,25 @@
         <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CH14" t="n">
         <v>1.34</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK14" t="n">
         <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM14" t="n">
         <v>2.06</v>
@@ -6415,20 +6415,20 @@
         <v>1.37</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX14" t="n">
         <v>1.81</v>
@@ -6446,22 +6446,22 @@
         <v>1.36</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="DE14" t="n">
         <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.40000000000001</v>
+        <v>84.67</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
@@ -6470,28 +6470,28 @@
         <v>3.06</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.64</v>
+        <v>38.43</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DO14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.18</v>
+        <v>5.27</v>
       </c>
       <c r="DS14" t="n">
         <v>0.22</v>
@@ -6503,28 +6503,28 @@
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.1</v>
+        <v>53.04</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.7</v>
+        <v>11.72</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.9</v>
       </c>
       <c r="EA14" t="n">
-        <v>9.06</v>
+        <v>9.19</v>
       </c>
       <c r="EB14" t="n">
         <v>1.3</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="15">
@@ -8509,13 +8509,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" t="n">
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
         <v>0.08</v>
@@ -8599,139 +8599,139 @@
         <v>3.12</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AI20" t="n">
-        <v>70.34999999999999</v>
+        <v>70.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="AK20" t="n">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="AL20" t="n">
         <v>4.15</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AN20" t="n">
-        <v>29.23</v>
+        <v>29.26</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AQ20" t="n">
         <v>11.04</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.62</v>
+        <v>7.67</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.73</v>
+        <v>7.81</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AV20" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AW20" t="n">
         <v>0.15</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0.12</v>
       </c>
       <c r="AX20" t="n">
         <v>0.04</v>
       </c>
       <c r="AY20" t="n">
-        <v>42.77</v>
+        <v>43.26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.19</v>
+        <v>10.26</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.380000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BE20" t="n">
         <v>1.07</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.210000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BP20" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="BR20" t="n">
-        <v>86.54000000000001</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="BS20" t="n">
-        <v>63.46</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="BT20" t="n">
-        <v>42.31</v>
+        <v>43.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>11.54</v>
+        <v>11.32</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.77</v>
+        <v>5.66</v>
       </c>
       <c r="BW20" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="BX20" t="n">
-        <v>48.08</v>
+        <v>49.06</v>
       </c>
       <c r="BY20" t="n">
         <v>2.07</v>
@@ -8740,46 +8740,46 @@
         <v>2.2</v>
       </c>
       <c r="CA20" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC20" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CD20" t="n">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="CE20" t="n">
         <v>1.47</v>
       </c>
       <c r="CF20" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CG20" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CH20" t="n">
         <v>1.31</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK20" t="n">
         <v>1.56</v>
       </c>
       <c r="CL20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM20" t="n">
         <v>2.23</v>
       </c>
       <c r="CN20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO20" t="n">
         <v>1.41</v>
@@ -8788,26 +8788,26 @@
         <v>2.25</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CR20" t="inlineStr"/>
       <c r="CS20" t="inlineStr"/>
       <c r="CT20" t="inlineStr"/>
       <c r="CU20" t="inlineStr"/>
       <c r="CV20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CX20" t="n">
         <v>1.79</v>
-      </c>
-      <c r="CW20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CX20" t="n">
-        <v>1.81</v>
       </c>
       <c r="CY20" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ20" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DA20" t="n">
         <v>1.8</v>
@@ -8816,64 +8816,64 @@
         <v>1.39</v>
       </c>
       <c r="DC20" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="DE20" t="n">
         <v>0.1</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="DH20" t="n">
-        <v>78.54000000000001</v>
+        <v>78.55</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM20" t="n">
-        <v>34.96</v>
+        <v>34.87</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.14</v>
+        <v>11.13</v>
       </c>
       <c r="DQ20" t="n">
-        <v>7.12</v>
+        <v>7.15</v>
       </c>
       <c r="DR20" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="DS20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DT20" t="n">
         <v>0.19</v>
-      </c>
-      <c r="DT20" t="n">
-        <v>0.18</v>
       </c>
       <c r="DU20" t="n">
         <v>0.02</v>
       </c>
       <c r="DV20" t="n">
-        <v>47.84</v>
+        <v>48</v>
       </c>
       <c r="DW20" t="n">
         <v>0.23</v>
@@ -8882,19 +8882,19 @@
         <v>12.38</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.35</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ20" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="EA20" t="n">
-        <v>10.69</v>
+        <v>10.81</v>
       </c>
       <c r="EB20" t="n">
         <v>1.31</v>
       </c>
       <c r="EC20" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>26</v>
@@ -1786,49 +1786,49 @@
         <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="H3" t="n">
-        <v>90.36</v>
+        <v>89.73</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>6.24</v>
+        <v>6.19</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>41.72</v>
+        <v>41</v>
       </c>
       <c r="N3" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="P3" t="n">
-        <v>11.6</v>
+        <v>11.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.6</v>
+        <v>6.77</v>
       </c>
       <c r="R3" t="n">
-        <v>4.6</v>
+        <v>4.77</v>
       </c>
       <c r="S3" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
         <v>0.08</v>
@@ -1840,28 +1840,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>55.72</v>
+        <v>55.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>15.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.04</v>
+        <v>5.96</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.32</v>
+        <v>8.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1945,64 +1945,64 @@
         <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="BH3" t="n">
         <v>9.33</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
         <v>0.73</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.23999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>72.55</v>
+        <v>73.08</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.29</v>
+        <v>36.54</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.84</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BV3" t="n">
-        <v>3.92</v>
+        <v>5.77</v>
       </c>
       <c r="BW3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="BY3" t="n">
         <v>1.96</v>
       </c>
-      <c r="BX3" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="CA3" t="n">
         <v>3.33</v>
@@ -2020,40 +2020,40 @@
         <v>1.47</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CG3" t="n">
         <v>2.52</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI3" t="n">
         <v>1.68</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK3" t="n">
         <v>1.57</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM3" t="n">
         <v>2.03</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO3" t="n">
         <v>1.38</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CR3" t="n">
         <v>1.68</v>
@@ -2067,7 +2067,7 @@
         <v>1.74</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CX3" t="n">
         <v>1.78</v>
@@ -2085,52 +2085,52 @@
         <v>1.43</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="DE3" t="n">
         <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DH3" t="n">
-        <v>89.63</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="DK3" t="n">
         <v>5.1</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="DM3" t="n">
-        <v>38.39</v>
+        <v>38.1</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.78</v>
+        <v>11.88</v>
       </c>
       <c r="DQ3" t="n">
-        <v>7.06</v>
+        <v>7.14</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.47</v>
+        <v>5.54</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.51</v>
+        <v>52.4</v>
       </c>
       <c r="DW3" t="n">
         <v>0.21</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.64</v>
+        <v>13.62</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.98</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="EA3" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="EB3" t="n">
         <v>1.46</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="4">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
         <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
         <v>0.13</v>
@@ -2266,136 +2266,136 @@
         <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AI4" t="n">
-        <v>83.86</v>
+        <v>83.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.36</v>
+        <v>37.09</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.09</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.91</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.41</v>
+        <v>4.61</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>49.36</v>
+        <v>49</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.23</v>
+        <v>11.09</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.45</v>
+        <v>7.43</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="BD4" t="n">
         <v>11</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BN4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.09</v>
       </c>
-      <c r="BO4" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BP4" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="BQ4" t="n">
         <v>4.22</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.67</v>
+        <v>84.78</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.89</v>
+        <v>67.39</v>
       </c>
       <c r="BT4" t="n">
-        <v>44.44</v>
+        <v>43.48</v>
       </c>
       <c r="BU4" t="n">
-        <v>15.56</v>
+        <v>15.22</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>44.44</v>
+        <v>43.48</v>
       </c>
       <c r="BY4" t="n">
         <v>1.98</v>
@@ -2407,22 +2407,22 @@
         <v>3.21</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CE4" t="n">
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH4" t="n">
         <v>1.29</v>
@@ -2446,23 +2446,23 @@
         <v>1.62</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="inlineStr"/>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="inlineStr"/>
       <c r="CV4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CX4" t="n">
         <v>1.81</v>
@@ -2480,52 +2480,52 @@
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="DE4" t="n">
         <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.40000000000001</v>
+        <v>88.22</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.98</v>
+        <v>4.93</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.22</v>
+        <v>40.02</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.29</v>
+        <v>11.2</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.91</v>
+        <v>7.05</v>
       </c>
       <c r="DR4" t="n">
-        <v>4.07</v>
+        <v>4.18</v>
       </c>
       <c r="DS4" t="n">
         <v>0.22</v>
@@ -2534,31 +2534,31 @@
         <v>0.18</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DV4" t="n">
-        <v>53.58</v>
+        <v>53.3</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.65</v>
+        <v>12.54</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.09</v>
+        <v>8.06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.55</v>
+        <v>4.47</v>
       </c>
       <c r="EA4" t="n">
-        <v>10.69</v>
+        <v>10.7</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="5">
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="n">
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2661,136 +2661,136 @@
         <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AH5" t="n">
         <v>2.88</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.48</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="AJ5" t="n">
         <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>37.32</v>
+        <v>37.46</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.84</v>
+        <v>10.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.96</v>
+        <v>8.31</v>
       </c>
       <c r="AS5" t="n">
         <v>5.88</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.44</v>
+        <v>54.38</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.72</v>
+        <v>13.85</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.08</v>
+        <v>9.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.279999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK5" t="n">
         <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>4.65</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.55</v>
+        <v>73.08</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.86</v>
+        <v>57.69</v>
       </c>
       <c r="BU5" t="n">
-        <v>25.49</v>
+        <v>26.92</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.73</v>
+        <v>15.38</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.84</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.82</v>
+        <v>59.62</v>
       </c>
       <c r="BY5" t="n">
         <v>1.53</v>
@@ -2799,16 +2799,16 @@
         <v>1.55</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CE5" t="n">
         <v>1.4</v>
@@ -2823,19 +2823,19 @@
         <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK5" t="n">
         <v>1.51</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN5" t="n">
         <v>1.72</v>
@@ -2857,7 +2857,7 @@
         <v>1.89</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
@@ -2874,49 +2874,49 @@
         <v>1.98</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.02</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.2</v>
+        <v>40.21</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.75</v>
+        <v>11.74</v>
       </c>
       <c r="DQ5" t="n">
-        <v>7.59</v>
+        <v>7.77</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="DS5" t="n">
         <v>0.27</v>
@@ -2928,28 +2928,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.79</v>
+        <v>56.71</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX5" t="n">
-        <v>16</v>
+        <v>16.02</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.43</v>
+        <v>10.46</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
       <c r="EA5" t="n">
-        <v>10.53</v>
+        <v>10.71</v>
       </c>
       <c r="EB5" t="n">
         <v>1.69</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="6">
@@ -3354,61 +3354,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="G7" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="H7" t="n">
-        <v>84.76000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="I7" t="n">
         <v>0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="K7" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
       <c r="L7" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>35.04</v>
+        <v>34.88</v>
       </c>
       <c r="N7" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>11.16</v>
+        <v>10.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.68</v>
+        <v>6.92</v>
       </c>
       <c r="R7" t="n">
-        <v>4.16</v>
+        <v>4.31</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="T7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
         <v>0.08</v>
@@ -3420,28 +3420,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.4</v>
+        <v>54.19</v>
       </c>
       <c r="Y7" t="n">
         <v>0.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.16</v>
+        <v>13.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.56</v>
+        <v>4.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.880000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AF7" t="n">
         <v>0.19</v>
@@ -3525,64 +3525,64 @@
         <v>2.12</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BH7" t="n">
         <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="BO7" t="n">
         <v>1.27</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="BR7" t="n">
-        <v>86.27</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>64.70999999999999</v>
+        <v>63.46</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.18</v>
+        <v>40.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>25.49</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.84</v>
+        <v>7.69</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BX7" t="n">
-        <v>49.02</v>
+        <v>48.08</v>
       </c>
       <c r="BY7" t="n">
         <v>1.94</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CA7" t="n">
         <v>3.27</v>
@@ -3600,13 +3600,13 @@
         <v>1.48</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI7" t="n">
         <v>1.67</v>
@@ -3621,7 +3621,7 @@
         <v>2.04</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN7" t="n">
         <v>1.54</v>
@@ -3630,10 +3630,10 @@
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="CR7" t="n">
         <v>1.68</v>
@@ -3647,7 +3647,7 @@
         <v>1.77</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX7" t="n">
         <v>1.83</v>
@@ -3662,55 +3662,55 @@
         <v>1.77</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="DE7" t="n">
         <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.02</v>
+        <v>80.67</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>34</v>
+        <v>33.94</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="DO7" t="n">
         <v>1.67</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6.51</v>
+        <v>6.64</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3722,28 +3722,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.2</v>
+        <v>53.12</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.18</v>
+        <v>12.1</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.94</v>
+        <v>7.93</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="EA7" t="n">
-        <v>9.529999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="8">
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" t="n">
         <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5435,139 +5435,139 @@
         <v>2.74</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>79.55</v>
+        <v>80.39</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.77</v>
+        <v>3.87</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.68</v>
+        <v>32.26</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.64</v>
+        <v>10.74</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AW12" t="n">
         <v>0.09</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AY12" t="n">
-        <v>52.86</v>
+        <v>52.78</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.32</v>
+        <v>12.17</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.77</v>
+        <v>8.65</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.82</v>
+        <v>10.22</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BO12" t="n">
         <v>1.02</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>89.13</v>
       </c>
       <c r="BS12" t="n">
-        <v>64.44</v>
+        <v>63.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>35.56</v>
+        <v>34.78</v>
       </c>
       <c r="BU12" t="n">
-        <v>17.78</v>
+        <v>17.39</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="BX12" t="n">
-        <v>40</v>
+        <v>39.13</v>
       </c>
       <c r="BY12" t="n">
         <v>2.39</v>
@@ -5576,25 +5576,25 @@
         <v>2.27</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CB12" t="n">
         <v>3.22</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CE12" t="n">
         <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CH12" t="n">
         <v>1.27</v>
@@ -5606,7 +5606,7 @@
         <v>2.04</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL12" t="n">
         <v>2.02</v>
@@ -5624,7 +5624,7 @@
         <v>2.26</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CR12" t="inlineStr"/>
       <c r="CS12" t="inlineStr"/>
@@ -5634,10 +5634,10 @@
         <v>1.73</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY12" t="n">
         <v>1.89</v>
@@ -5649,58 +5649,58 @@
         <v>1.8</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DD12" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="DE12" t="n">
         <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.38</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.51</v>
+        <v>32.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.13</v>
+        <v>10.2</v>
       </c>
       <c r="DQ12" t="n">
-        <v>6.64</v>
+        <v>6.59</v>
       </c>
       <c r="DR12" t="n">
         <v>4.93</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
         <v>0.13</v>
@@ -5709,28 +5709,28 @@
         <v>0.02</v>
       </c>
       <c r="DV12" t="n">
-        <v>52.2</v>
+        <v>52.18</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.51</v>
+        <v>12.44</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.710000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="EA12" t="n">
-        <v>10.62</v>
+        <v>10.81</v>
       </c>
       <c r="EB12" t="n">
         <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="13">
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
         <v>27</v>
@@ -5752,79 +5752,79 @@
         <v>0.15</v>
       </c>
       <c r="F13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H13" t="n">
-        <v>95.31</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="K13" t="n">
-        <v>5.58</v>
+        <v>5.59</v>
       </c>
       <c r="L13" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="M13" t="n">
-        <v>44.27</v>
+        <v>44.37</v>
       </c>
       <c r="N13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O13" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="P13" t="n">
-        <v>12.42</v>
+        <v>12.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.04</v>
+        <v>6.93</v>
       </c>
       <c r="R13" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="S13" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>59.65</v>
+        <v>59.33</v>
       </c>
       <c r="Y13" t="n">
         <v>0.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.38</v>
+        <v>17.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.69</v>
+        <v>11.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.15</v>
+        <v>8.52</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AE13" t="n">
         <v>2.96</v>
@@ -5911,70 +5911,70 @@
         <v>2.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.869999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN13" t="n">
         <v>1.28</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
         <v>3.87</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.68000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.81</v>
+        <v>70.37</v>
       </c>
       <c r="BT13" t="n">
-        <v>41.51</v>
+        <v>42.59</v>
       </c>
       <c r="BU13" t="n">
-        <v>20.75</v>
+        <v>20.37</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.32</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.55</v>
+        <v>7.41</v>
       </c>
       <c r="BX13" t="n">
-        <v>50.94</v>
+        <v>51.85</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CA13" t="n">
         <v>3.33</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC13" t="n">
         <v>2.52</v>
@@ -5986,10 +5986,10 @@
         <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH13" t="n">
         <v>1.31</v>
@@ -5998,13 +5998,13 @@
         <v>1.7</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
         <v>1.49</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM13" t="n">
         <v>2.01</v>
@@ -6016,10 +6016,10 @@
         <v>1.32</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CR13" t="n">
         <v>1.68</v>
@@ -6030,10 +6030,10 @@
       </c>
       <c r="CU13" t="inlineStr"/>
       <c r="CV13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX13" t="n">
         <v>1.77</v>
@@ -6051,22 +6051,22 @@
         <v>1.36</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="DE13" t="n">
         <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DH13" t="n">
-        <v>93.17</v>
+        <v>93.42</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
@@ -6075,55 +6075,55 @@
         <v>3.3</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.3</v>
+        <v>43.37</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DP13" t="n">
         <v>11.13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.85</v>
+        <v>56.74</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.88</v>
+        <v>15.87</v>
       </c>
       <c r="DY13" t="n">
-        <v>10.6</v>
+        <v>10.56</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>9.09</v>
+        <v>9.26</v>
       </c>
       <c r="EB13" t="n">
         <v>1.69</v>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" t="n">
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
         <v>0.23</v>
@@ -6232,136 +6232,136 @@
         <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
-        <v>82.12</v>
+        <v>81.88</v>
       </c>
       <c r="AJ14" t="n">
         <v>0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>34.04</v>
+        <v>33.77</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.76</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.08</v>
+        <v>6.35</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.48</v>
+        <v>50.42</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.76</v>
+        <v>10.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.02</v>
+        <v>8.98</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN14" t="n">
         <v>1.35</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BP14" t="n">
         <v>4.1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.16</v>
+        <v>92.31</v>
       </c>
       <c r="BS14" t="n">
-        <v>72.55</v>
+        <v>73.08</v>
       </c>
       <c r="BT14" t="n">
-        <v>45.1</v>
+        <v>46.15</v>
       </c>
       <c r="BU14" t="n">
-        <v>19.61</v>
+        <v>19.23</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BX14" t="n">
-        <v>54.9</v>
+        <v>55.77</v>
       </c>
       <c r="BY14" t="n">
         <v>1.84</v>
@@ -6373,19 +6373,19 @@
         <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="CE14" t="n">
         <v>1.44</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CG14" t="n">
         <v>2.63</v>
@@ -6397,13 +6397,13 @@
         <v>1.76</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK14" t="n">
         <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM14" t="n">
         <v>2.06</v>
@@ -6418,17 +6418,17 @@
         <v>2.13</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX14" t="n">
         <v>1.81</v>
@@ -6443,88 +6443,88 @@
         <v>1.76</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="DE14" t="n">
         <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.67</v>
+        <v>84.5</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="DL14" t="n">
         <v>0.23</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.43</v>
+        <v>38.21</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.16</v>
+        <v>10.04</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.27</v>
+        <v>5.43</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU14" t="n">
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.04</v>
+        <v>52.96</v>
       </c>
       <c r="DW14" t="n">
         <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.72</v>
+        <v>11.63</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.82</v>
+        <v>7.77</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="EA14" t="n">
-        <v>9.19</v>
+        <v>9.4</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="15">
@@ -8509,94 +8509,94 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" t="n">
         <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="G20" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="H20" t="n">
-        <v>86.73</v>
+        <v>87.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="K20" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="L20" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="M20" t="n">
-        <v>40.69</v>
+        <v>40.74</v>
       </c>
       <c r="N20" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="P20" t="n">
-        <v>11.23</v>
+        <v>11.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="R20" t="n">
-        <v>4.27</v>
+        <v>4.48</v>
       </c>
       <c r="S20" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="U20" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="V20" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>52.92</v>
+        <v>53.15</v>
       </c>
       <c r="Y20" t="n">
         <v>0.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.58</v>
+        <v>14.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.81</v>
+        <v>9.93</v>
       </c>
       <c r="AB20" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>12.48</v>
       </c>
       <c r="AD20" t="n">
         <v>1.55</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="n">
         <v>0.11</v>
@@ -8680,70 +8680,70 @@
         <v>3.26</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BH20" t="n">
-        <v>9.26</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="BN20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BP20" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
       <c r="BR20" t="n">
-        <v>86.79000000000001</v>
+        <v>85.19</v>
       </c>
       <c r="BS20" t="n">
-        <v>64.15000000000001</v>
+        <v>62.96</v>
       </c>
       <c r="BT20" t="n">
-        <v>43.4</v>
+        <v>42.59</v>
       </c>
       <c r="BU20" t="n">
-        <v>11.32</v>
+        <v>11.11</v>
       </c>
       <c r="BV20" t="n">
-        <v>5.66</v>
+        <v>5.56</v>
       </c>
       <c r="BW20" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="BX20" t="n">
-        <v>49.06</v>
+        <v>48.15</v>
       </c>
       <c r="BY20" t="n">
         <v>2.07</v>
       </c>
       <c r="BZ20" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CA20" t="n">
         <v>3.21</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC20" t="n">
         <v>3.62</v>
@@ -8752,7 +8752,7 @@
         <v>4.52</v>
       </c>
       <c r="CE20" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF20" t="n">
         <v>3.2</v>
@@ -8767,7 +8767,7 @@
         <v>1.71</v>
       </c>
       <c r="CJ20" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK20" t="n">
         <v>1.56</v>
@@ -8785,10 +8785,10 @@
         <v>1.41</v>
       </c>
       <c r="CP20" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CQ20" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="CR20" t="inlineStr"/>
       <c r="CS20" t="inlineStr"/>
@@ -8801,7 +8801,7 @@
         <v>2.02</v>
       </c>
       <c r="CX20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CY20" t="n">
         <v>1.88</v>
@@ -8819,82 +8819,82 @@
         <v>2.25</v>
       </c>
       <c r="DD20" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="DG20" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="DH20" t="n">
-        <v>78.55</v>
+        <v>78.89</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="DK20" t="n">
-        <v>4.81</v>
+        <v>4.8</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM20" t="n">
-        <v>34.87</v>
+        <v>35</v>
       </c>
       <c r="DN20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DO20" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DP20" t="n">
-        <v>11.13</v>
+        <v>11.15</v>
       </c>
       <c r="DQ20" t="n">
-        <v>7.15</v>
+        <v>7.17</v>
       </c>
       <c r="DR20" t="n">
-        <v>6.07</v>
+        <v>6.14</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU20" t="n">
         <v>0.02</v>
       </c>
       <c r="DV20" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX20" t="n">
-        <v>12.38</v>
+        <v>12.46</v>
       </c>
       <c r="DY20" t="n">
-        <v>8.380000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ20" t="n">
         <v>4</v>
       </c>
       <c r="EA20" t="n">
-        <v>10.81</v>
+        <v>11.08</v>
       </c>
       <c r="EB20" t="n">
         <v>1.31</v>
       </c>
       <c r="EC20" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
         <v>0.19</v>
@@ -3447,49 +3447,49 @@
         <v>0.19</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AI7" t="n">
-        <v>77.42</v>
+        <v>78</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="AM7" t="n">
         <v>0.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>33</v>
+        <v>33.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.35</v>
+        <v>6.74</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.62</v>
+        <v>5.59</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3501,82 +3501,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.04</v>
+        <v>52.44</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.35</v>
+        <v>6.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>10.15</v>
+        <v>11.11</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="BH7" t="n">
-        <v>8</v>
+        <v>8.02</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="BN7" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="BR7" t="n">
-        <v>86.54000000000001</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>63.46</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>40.38</v>
+        <v>41.51</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>24.53</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.69</v>
+        <v>7.55</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BX7" t="n">
-        <v>48.08</v>
+        <v>47.17</v>
       </c>
       <c r="BY7" t="n">
         <v>1.94</v>
@@ -3588,10 +3588,10 @@
         <v>3.27</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CD7" t="n">
         <v>3.71</v>
@@ -3612,13 +3612,13 @@
         <v>1.67</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CK7" t="n">
         <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM7" t="n">
         <v>1.9</v>
@@ -3633,7 +3633,7 @@
         <v>2.29</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="CR7" t="n">
         <v>1.68</v>
@@ -3644,31 +3644,31 @@
       </c>
       <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY7" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DA7" t="n">
         <v>1.77</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="DE7" t="n">
         <v>0.19</v>
@@ -3677,37 +3677,37 @@
         <v>1.36</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.67</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="DL7" t="n">
         <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.94</v>
+        <v>34.26</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.1</v>
+        <v>10.08</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6.64</v>
+        <v>6.83</v>
       </c>
       <c r="DR7" t="n">
         <v>4.96</v>
@@ -3722,28 +3722,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.12</v>
+        <v>53.3</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.93</v>
+        <v>7.94</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="EA7" t="n">
-        <v>9.640000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
@@ -6139,94 +6139,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
         <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="F14" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="G14" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>87.12</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0.04</v>
       </c>
       <c r="J14" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="K14" t="n">
-        <v>5.23</v>
+        <v>5.15</v>
       </c>
       <c r="L14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="M14" t="n">
-        <v>42.65</v>
+        <v>42.59</v>
       </c>
       <c r="N14" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="O14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="P14" t="n">
-        <v>10.54</v>
+        <v>10.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.42</v>
+        <v>6.52</v>
       </c>
       <c r="R14" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="U14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="V14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="W14" t="n">
         <v>0.04</v>
       </c>
       <c r="X14" t="n">
-        <v>55.5</v>
+        <v>54.81</v>
       </c>
       <c r="Y14" t="n">
         <v>0.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.38</v>
+        <v>13.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.81</v>
+        <v>8.59</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.65</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6310,70 +6310,70 @@
         <v>2.62</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BH14" t="n">
         <v>8.98</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="BK14" t="n">
         <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.31</v>
+        <v>92.45</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.08</v>
+        <v>73.58</v>
       </c>
       <c r="BT14" t="n">
-        <v>46.15</v>
+        <v>47.17</v>
       </c>
       <c r="BU14" t="n">
-        <v>19.23</v>
+        <v>18.87</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.619999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="BX14" t="n">
-        <v>55.77</v>
+        <v>54.72</v>
       </c>
       <c r="BY14" t="n">
         <v>1.84</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CA14" t="n">
         <v>3.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>3.73</v>
@@ -6394,7 +6394,7 @@
         <v>1.34</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ14" t="n">
         <v>2.01</v>
@@ -6403,7 +6403,7 @@
         <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM14" t="n">
         <v>2.06</v>
@@ -6412,10 +6412,10 @@
         <v>1.64</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ14" t="n">
         <v>3.84</v>
@@ -6425,73 +6425,73 @@
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CY14" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DA14" t="n">
         <v>1.76</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.5</v>
+        <v>84.36</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.21</v>
+        <v>38.26</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.04</v>
+        <v>10.17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.71</v>
+        <v>7.74</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.43</v>
+        <v>5.45</v>
       </c>
       <c r="DS14" t="n">
         <v>0.21</v>
@@ -6503,28 +6503,28 @@
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.96</v>
+        <v>52.66</v>
       </c>
       <c r="DW14" t="n">
         <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.63</v>
+        <v>11.58</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.77</v>
+        <v>7.68</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="EA14" t="n">
-        <v>9.4</v>
+        <v>9.41</v>
       </c>
       <c r="EB14" t="n">
         <v>1.29</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>27</v>
@@ -3366,82 +3366,82 @@
         <v>0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="H7" t="n">
-        <v>83.92</v>
+        <v>87.89</v>
       </c>
       <c r="I7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="K7" t="n">
-        <v>4.38</v>
+        <v>4.63</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>34.88</v>
+        <v>38.22</v>
       </c>
       <c r="N7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="P7" t="n">
-        <v>10.88</v>
+        <v>10.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.92</v>
+        <v>7.04</v>
       </c>
       <c r="R7" t="n">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="S7" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.19</v>
+        <v>54.89</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.92</v>
+        <v>14.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AF7" t="n">
         <v>0.19</v>
@@ -3525,70 +3525,70 @@
         <v>2.11</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.02</v>
+        <v>8.09</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="BL7" t="n">
         <v>0.43</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="BO7" t="n">
         <v>1.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>86.79000000000001</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>64.15000000000001</v>
+        <v>62.96</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.51</v>
+        <v>40.74</v>
       </c>
       <c r="BU7" t="n">
-        <v>24.53</v>
+        <v>24.07</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.55</v>
+        <v>7.41</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.17</v>
+        <v>46.3</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CA7" t="n">
         <v>3.27</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CC7" t="n">
         <v>3.25</v>
@@ -3597,10 +3597,10 @@
         <v>3.71</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CG7" t="n">
         <v>2.49</v>
@@ -3609,13 +3609,13 @@
         <v>1.3</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ7" t="n">
         <v>2.12</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
         <v>2.05</v>
@@ -3624,16 +3624,16 @@
         <v>1.9</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO7" t="n">
         <v>1.37</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="CR7" t="n">
         <v>1.68</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW7" t="n">
         <v>2.07</v>
@@ -3665,52 +3665,52 @@
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DE7" t="n">
         <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.90000000000001</v>
+        <v>82.94</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.26</v>
+        <v>35.94</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.08</v>
+        <v>10.12</v>
       </c>
       <c r="DQ7" t="n">
-        <v>6.83</v>
+        <v>6.89</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3722,28 +3722,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.3</v>
+        <v>53.66</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.09</v>
+        <v>12.54</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.94</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="EA7" t="n">
-        <v>10.13</v>
+        <v>10.46</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="8">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" t="n">
         <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" t="n">
         <v>0.26</v>
@@ -6229,49 +6229,49 @@
         <v>2.37</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AI14" t="n">
-        <v>81.88</v>
+        <v>82.41</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AN14" t="n">
-        <v>33.77</v>
+        <v>33.81</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.539999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.35</v>
+        <v>6.89</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AU14" t="n">
         <v>1.15</v>
@@ -6286,82 +6286,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.42</v>
+        <v>49.56</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.880000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.73</v>
+        <v>6.52</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.15</v>
+        <v>10.11</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.98</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO14" t="n">
         <v>1.11</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.72</v>
+        <v>4.76</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.45</v>
+        <v>92.59</v>
       </c>
       <c r="BS14" t="n">
-        <v>73.58</v>
+        <v>72.22</v>
       </c>
       <c r="BT14" t="n">
-        <v>47.17</v>
+        <v>46.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.87</v>
+        <v>18.52</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.43</v>
+        <v>9.26</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BX14" t="n">
-        <v>54.72</v>
+        <v>53.7</v>
       </c>
       <c r="BY14" t="n">
         <v>1.84</v>
@@ -6379,7 +6379,7 @@
         <v>3.73</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.03</v>
+        <v>4.09</v>
       </c>
       <c r="CE14" t="n">
         <v>1.44</v>
@@ -6403,13 +6403,13 @@
         <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM14" t="n">
         <v>2.06</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO14" t="n">
         <v>1.36</v>
@@ -6418,7 +6418,7 @@
         <v>2.12</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="inlineStr"/>
@@ -6452,79 +6452,79 @@
         <v>3.81</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.36</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.51</v>
+        <v>4.44</v>
       </c>
       <c r="DL14" t="n">
         <v>0.22</v>
       </c>
       <c r="DM14" t="n">
-        <v>38.26</v>
+        <v>38.2</v>
       </c>
       <c r="DN14" t="n">
         <v>1.22</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DP14" t="n">
         <v>10.17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>7.74</v>
+        <v>7.82</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.45</v>
+        <v>5.74</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU14" t="n">
         <v>0.02</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.66</v>
+        <v>52.18</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.58</v>
+        <v>11.42</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.68</v>
+        <v>7.56</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="EA14" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -3644,7 +3644,7 @@
       </c>
       <c r="CU7" t="inlineStr"/>
       <c r="CV7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW7" t="n">
         <v>2.07</v>
@@ -3665,10 +3665,10 @@
         <v>1.43</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="DE7" t="n">
         <v>0.19</v>
@@ -6244,7 +6244,7 @@
         <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="AL14" t="n">
         <v>3.74</v>
@@ -6256,7 +6256,7 @@
         <v>33.81</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AP14" t="n">
         <v>1.89</v>
@@ -6307,7 +6307,7 @@
         <v>1.08</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="BG14" t="n">
         <v>2.41</v>
@@ -6379,7 +6379,7 @@
         <v>3.73</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="CE14" t="n">
         <v>1.44</v>
@@ -6446,10 +6446,10 @@
         <v>1.36</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="DE14" t="n">
         <v>0.18</v>
@@ -6467,7 +6467,7 @@
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="DK14" t="n">
         <v>4.44</v>
@@ -6479,7 +6479,7 @@
         <v>38.2</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="DO14" t="n">
         <v>1.89</v>
@@ -6524,7 +6524,7 @@
         <v>1.28</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -1870,7 +1870,7 @@
         <v>1.73</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="AI3" t="n">
         <v>88.92</v>
@@ -1885,7 +1885,7 @@
         <v>4</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="AN3" t="n">
         <v>35.19</v>
@@ -1894,7 +1894,7 @@
         <v>0.96</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ3" t="n">
         <v>11.96</v>
@@ -1972,10 +1972,10 @@
         <v>0.92</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.13</v>
+        <v>4.31</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.25</v>
+        <v>4.37</v>
       </c>
       <c r="BR3" t="n">
         <v>88.45999999999999</v>
@@ -2097,7 +2097,7 @@
         <v>1.77</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DH3" t="n">
         <v>89.31999999999999</v>
@@ -2112,7 +2112,7 @@
         <v>5.1</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
         <v>38.1</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="DP3" t="n">
         <v>11.88</v>
@@ -2248,22 +2248,22 @@
         <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.3</v>
+        <v>5.26</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.39</v>
+        <v>10.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
         <v>3.26</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="AG4" t="n">
         <v>2</v>
@@ -2308,7 +2308,7 @@
         <v>1.04</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AV4" t="n">
         <v>0.13</v>
@@ -2344,19 +2344,19 @@
         <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BH4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
         <v>0.67</v>
@@ -2368,7 +2368,7 @@
         <v>1.07</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BP4" t="n">
         <v>4.22</v>
@@ -2380,10 +2380,10 @@
         <v>84.78</v>
       </c>
       <c r="BS4" t="n">
-        <v>67.39</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.48</v>
+        <v>45.65</v>
       </c>
       <c r="BU4" t="n">
         <v>15.22</v>
@@ -2486,7 +2486,7 @@
         <v>4.35</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
         <v>1.98</v>
@@ -2546,13 +2546,13 @@
         <v>12.54</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.06</v>
+        <v>8.08</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="EA4" t="n">
-        <v>10.7</v>
+        <v>10.72</v>
       </c>
       <c r="EB4" t="n">
         <v>1.4</v>
@@ -2577,13 +2577,13 @@
         <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="H5" t="n">
         <v>97.34999999999999</v>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="K5" t="n">
         <v>6.19</v>
       </c>
       <c r="L5" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>42.96</v>
@@ -2607,7 +2607,7 @@
         <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
         <v>12.62</v>
@@ -2619,7 +2619,7 @@
         <v>4.54</v>
       </c>
       <c r="S5" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="T5" t="n">
         <v>1.96</v>
@@ -2637,7 +2637,7 @@
         <v>59.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
         <v>18.19</v>
@@ -2661,7 +2661,7 @@
         <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="n">
         <v>2.88</v>
@@ -2673,7 +2673,7 @@
         <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AL5" t="n">
         <v>5.35</v>
@@ -2736,22 +2736,22 @@
         <v>1.47</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="BH5" t="n">
         <v>9.619999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="BL5" t="n">
         <v>0.79</v>
@@ -2763,22 +2763,22 @@
         <v>1.25</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.65</v>
+        <v>4.77</v>
       </c>
       <c r="BR5" t="n">
         <v>88.45999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>73.08</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.69</v>
+        <v>59.62</v>
       </c>
       <c r="BU5" t="n">
         <v>26.92</v>
@@ -2877,13 +2877,13 @@
         <v>3.39</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="DF5" t="n">
         <v>1.48</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="DH5" t="n">
         <v>92.15000000000001</v>
@@ -2892,13 +2892,13 @@
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="DK5" t="n">
         <v>5.77</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="DM5" t="n">
         <v>40.21</v>
@@ -2907,7 +2907,7 @@
         <v>1.4</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="DP5" t="n">
         <v>11.74</v>
@@ -2931,7 +2931,7 @@
         <v>56.71</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="DX5" t="n">
         <v>16.02</v>
@@ -2949,7 +2949,7 @@
         <v>1.69</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -4160,7 +4160,7 @@
         <v>0.15</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="G9" t="n">
         <v>1.4</v>
@@ -4172,7 +4172,7 @@
         <v>0.25</v>
       </c>
       <c r="J9" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
         <v>4.25</v>
@@ -4235,7 +4235,7 @@
         <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AF9" t="n">
         <v>0.1</v>
@@ -4472,7 +4472,7 @@
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DG9" t="n">
         <v>1.68</v>
@@ -4484,7 +4484,7 @@
         <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="DK9" t="n">
         <v>3.85</v>
@@ -4541,7 +4541,7 @@
         <v>1.2</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -4608,10 +4608,10 @@
         <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="V10" t="n">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -4910,10 +4910,10 @@
         <v>4.32</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
         <v>0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="G11" t="n">
         <v>2.1</v>
@@ -4974,7 +4974,7 @@
         <v>0.2</v>
       </c>
       <c r="J11" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
         <v>4.3</v>
@@ -5037,13 +5037,13 @@
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
         <v>0.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AH11" t="n">
         <v>1.1</v>
@@ -5055,7 +5055,7 @@
         <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AL11" t="n">
         <v>2.8</v>
@@ -5067,7 +5067,7 @@
         <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AP11" t="n">
         <v>1.55</v>
@@ -5100,7 +5100,7 @@
         <v>37.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="BA11" t="n">
         <v>10.4</v>
@@ -5118,7 +5118,7 @@
         <v>1.02</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="BG11" t="n">
         <v>2.12</v>
@@ -5266,7 +5266,7 @@
         <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="DG11" t="n">
         <v>1.6</v>
@@ -5278,7 +5278,7 @@
         <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="DK11" t="n">
         <v>3.55</v>
@@ -5290,7 +5290,7 @@
         <v>30.75</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DO11" t="n">
         <v>1.88</v>
@@ -5317,7 +5317,7 @@
         <v>43.15</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
         <v>10.6</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G12" t="n">
         <v>2.52</v>
@@ -5369,7 +5369,7 @@
         <v>0.13</v>
       </c>
       <c r="J12" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="K12" t="n">
         <v>5.39</v>
@@ -5432,7 +5432,7 @@
         <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AF12" t="n">
         <v>0.04</v>
@@ -5510,7 +5510,7 @@
         <v>10.22</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BF12" t="n">
         <v>2</v>
@@ -5661,7 +5661,7 @@
         <v>0.02</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DG12" t="n">
         <v>2.31</v>
@@ -5673,7 +5673,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DK12" t="n">
         <v>4.63</v>
@@ -5727,10 +5727,10 @@
         <v>10.81</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="13">
@@ -5833,7 +5833,7 @@
         <v>0.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="n">
         <v>2.26</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="AL13" t="n">
         <v>5.37</v>
@@ -5890,7 +5890,7 @@
         <v>54.15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BA13" t="n">
         <v>14.44</v>
@@ -5908,7 +5908,7 @@
         <v>1.56</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="BG13" t="n">
         <v>2.44</v>
@@ -6060,7 +6060,7 @@
         <v>0.13</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="DG13" t="n">
         <v>2.35</v>
@@ -6072,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="DK13" t="n">
         <v>5.48</v>
@@ -6111,7 +6111,7 @@
         <v>56.74</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DX13" t="n">
         <v>15.87</v>
@@ -6129,7 +6129,7 @@
         <v>1.69</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="14">
@@ -6546,7 +6546,7 @@
         <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
         <v>1.85</v>
@@ -6558,7 +6558,7 @@
         <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
         <v>4.05</v>
@@ -6621,7 +6621,7 @@
         <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0.11</v>
@@ -6663,7 +6663,7 @@
         <v>6.79</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="AT15" t="n">
         <v>2.11</v>
@@ -6687,19 +6687,19 @@
         <v>0.21</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.16</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.21</v>
+        <v>7.05</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BF15" t="n">
         <v>2.79</v>
@@ -6854,7 +6854,7 @@
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DG15" t="n">
         <v>1.77</v>
@@ -6866,7 +6866,7 @@
         <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="DK15" t="n">
         <v>3.87</v>
@@ -6890,7 +6890,7 @@
         <v>6.74</v>
       </c>
       <c r="DR15" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="DS15" t="n">
         <v>0.02</v>
@@ -6908,22 +6908,22 @@
         <v>0.36</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.56</v>
+        <v>7.49</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="EA15" t="n">
-        <v>9.69</v>
+        <v>9.66</v>
       </c>
       <c r="EB15" t="n">
         <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="16">
@@ -7017,7 +7017,7 @@
         <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE16" t="n">
         <v>2.15</v>
@@ -7315,7 +7315,7 @@
         <v>8.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="EC16" t="n">
         <v>2.33</v>
@@ -7421,7 +7421,7 @@
         <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
         <v>1.35</v>
@@ -7433,7 +7433,7 @@
         <v>0.35</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="AL17" t="n">
         <v>3.48</v>
@@ -7496,7 +7496,7 @@
         <v>1.29</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG17" t="n">
         <v>2.28</v>
@@ -7644,7 +7644,7 @@
         <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="DG17" t="n">
         <v>1.94</v>
@@ -7656,7 +7656,7 @@
         <v>0.22</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="DK17" t="n">
         <v>4.46</v>
@@ -7713,7 +7713,7 @@
         <v>1.5</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="18">
@@ -7816,7 +7816,7 @@
         <v>0.04</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AH18" t="n">
         <v>1.74</v>
@@ -7828,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="AL18" t="n">
         <v>3.39</v>
@@ -7891,7 +7891,7 @@
         <v>1.12</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BG18" t="n">
         <v>2.26</v>
@@ -8035,7 +8035,7 @@
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DG18" t="n">
         <v>2.39</v>
@@ -8047,7 +8047,7 @@
         <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="DK18" t="n">
         <v>4.46</v>
@@ -8104,7 +8104,7 @@
         <v>1.38</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -8126,7 +8126,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G19" t="n">
         <v>1.85</v>
@@ -8138,7 +8138,7 @@
         <v>-0.05</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="K19" t="n">
         <v>4.8</v>
@@ -8201,7 +8201,7 @@
         <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AF19" t="n">
         <v>0.05</v>
@@ -8430,7 +8430,7 @@
         <v>0.02</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DG19" t="n">
         <v>2.15</v>
@@ -8442,7 +8442,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DK19" t="n">
         <v>4.75</v>
@@ -8499,7 +8499,7 @@
         <v>1.32</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="20">
@@ -8602,7 +8602,7 @@
         <v>0.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AH20" t="n">
         <v>1.96</v>
@@ -8614,7 +8614,7 @@
         <v>0.19</v>
       </c>
       <c r="AK20" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="AL20" t="n">
         <v>4.15</v>
@@ -8677,7 +8677,7 @@
         <v>1.07</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="BG20" t="n">
         <v>2.17</v>
@@ -8825,7 +8825,7 @@
         <v>0.09</v>
       </c>
       <c r="DF20" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DG20" t="n">
         <v>2.52</v>
@@ -8837,7 +8837,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ20" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="DK20" t="n">
         <v>4.8</v>
@@ -8894,7 +8894,7 @@
         <v>1.31</v>
       </c>
       <c r="EC20" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="21">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -4373,13 +4373,13 @@
         <v>45</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="BZ9" t="n">
         <v>3.22</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="CB9" t="n">
         <v>3.49</v>
@@ -4391,43 +4391,43 @@
         <v>5.89</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="CI9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CK9" t="n">
         <v>1.6</v>
       </c>
-      <c r="CJ9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1.64</v>
-      </c>
       <c r="CL9" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="CR9" t="n">
         <v>1.72</v>
@@ -4782,7 +4782,7 @@
         <v>2.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.21</v>
+        <v>3.01</v>
       </c>
       <c r="CB10" t="n">
         <v>3.64</v>
@@ -4794,43 +4794,43 @@
         <v>5.26</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="n">

--- a/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
+++ b/data/teams/leagues/Averages_Colombia_Primera_Liga_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
